--- a/research/traditional_assets/database/data/switzerland/switzerland_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_hospitals_healthcare_facilities.xlsx
@@ -588,118 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0506</v>
+        <v>0.0989</v>
+      </c>
+      <c r="E2">
+        <v>0.29</v>
       </c>
       <c r="G2">
-        <v>0.01900439653949794</v>
+        <v>0.03138052907786227</v>
       </c>
       <c r="H2">
-        <v>0.01900439653949794</v>
+        <v>0.03138052907786227</v>
       </c>
       <c r="I2">
-        <v>-0.3678767057929631</v>
+        <v>-0.1892694513123313</v>
       </c>
       <c r="J2">
-        <v>-0.3678767057929631</v>
+        <v>-0.1887026037170304</v>
       </c>
       <c r="K2">
-        <v>-3.71</v>
+        <v>30.6</v>
       </c>
       <c r="L2">
-        <v>-0.005261665012055028</v>
+        <v>0.03277283924172646</v>
       </c>
       <c r="M2">
-        <v>2.3</v>
+        <v>40.8</v>
       </c>
       <c r="N2">
-        <v>0.001718855093042374</v>
+        <v>0.02551275637818909</v>
       </c>
       <c r="O2">
-        <v>-0.6199460916442048</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02213606803401701</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>1.156862745098039</v>
       </c>
       <c r="S2">
-        <v>2.3</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>0.1323529411764706</v>
       </c>
       <c r="U2">
-        <v>101.9</v>
+        <v>72.5</v>
       </c>
       <c r="V2">
-        <v>0.07615275390479039</v>
+        <v>0.04533516758379189</v>
       </c>
       <c r="W2">
-        <v>-0.009970438054286481</v>
+        <v>0.05932531989143079</v>
       </c>
       <c r="X2">
-        <v>0.08883360584328018</v>
+        <v>0.1106329852176671</v>
       </c>
       <c r="Y2">
-        <v>-0.09880404389756665</v>
+        <v>-0.05130766532623633</v>
       </c>
       <c r="Z2">
-        <v>0.2812693976499439</v>
+        <v>0.3735391038295949</v>
       </c>
       <c r="AA2">
-        <v>-0.1034724594478323</v>
+        <v>-0.07048780148277073</v>
       </c>
       <c r="AB2">
-        <v>0.04481703761767163</v>
+        <v>0.0691974671216551</v>
       </c>
       <c r="AC2">
-        <v>-0.148289497065504</v>
+        <v>-0.1396852686044258</v>
       </c>
       <c r="AD2">
-        <v>869.1</v>
+        <v>962.3</v>
       </c>
       <c r="AE2">
-        <v>1490.949326273092</v>
+        <v>1216.604433451619</v>
       </c>
       <c r="AF2">
-        <v>2360.049326273092</v>
+        <v>2178.904433451619</v>
       </c>
       <c r="AG2">
-        <v>2258.149326273091</v>
+        <v>2106.404433451619</v>
       </c>
       <c r="AH2">
-        <v>0.6381703706517157</v>
+        <v>0.5767189530706023</v>
       </c>
       <c r="AI2">
-        <v>0.8037358856306588</v>
+        <v>0.7735102432217611</v>
       </c>
       <c r="AJ2">
-        <v>0.6279179004013284</v>
+        <v>0.568437476606101</v>
       </c>
       <c r="AK2">
-        <v>0.7966800836204208</v>
+        <v>0.7675269751704956</v>
       </c>
       <c r="AL2">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="AM2">
-        <v>19.4</v>
+        <v>18.82</v>
       </c>
       <c r="AN2">
-        <v>9.158061116965227</v>
+        <v>7.785598705501617</v>
       </c>
       <c r="AO2">
-        <v>-1.79126213592233</v>
+        <v>-0.6305418719211823</v>
       </c>
       <c r="AP2">
-        <v>23.79504031899991</v>
+        <v>17.04210706676067</v>
       </c>
       <c r="AQ2">
-        <v>-1.902061855670103</v>
+        <v>-0.6801275239107333</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0506</v>
+        <v>0.0989</v>
+      </c>
+      <c r="E3">
+        <v>0.29</v>
       </c>
       <c r="G3">
-        <v>0.01900439653949794</v>
+        <v>0.03138052907786227</v>
       </c>
       <c r="H3">
-        <v>0.01900439653949794</v>
+        <v>0.03138052907786227</v>
       </c>
       <c r="I3">
-        <v>-0.3678767057929631</v>
+        <v>-0.1892694513123313</v>
       </c>
       <c r="J3">
-        <v>-0.3678767057929631</v>
+        <v>-0.1887026037170304</v>
       </c>
       <c r="K3">
-        <v>-3.71</v>
+        <v>30.6</v>
       </c>
       <c r="L3">
-        <v>-0.005261665012055028</v>
+        <v>0.03277283924172646</v>
       </c>
       <c r="M3">
-        <v>2.3</v>
+        <v>40.8</v>
       </c>
       <c r="N3">
-        <v>0.001718855093042374</v>
+        <v>0.02551275637818909</v>
       </c>
       <c r="O3">
-        <v>-0.6199460916442048</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>35.4</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02213606803401701</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.156862745098039</v>
       </c>
       <c r="S3">
-        <v>2.3</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.1323529411764706</v>
       </c>
       <c r="U3">
-        <v>101.9</v>
+        <v>72.5</v>
       </c>
       <c r="V3">
-        <v>0.07615275390479039</v>
+        <v>0.04533516758379189</v>
       </c>
       <c r="W3">
-        <v>-0.009970438054286481</v>
+        <v>0.05932531989143079</v>
       </c>
       <c r="X3">
-        <v>0.08883360584328018</v>
+        <v>0.1106329852176671</v>
       </c>
       <c r="Y3">
-        <v>-0.09880404389756665</v>
+        <v>-0.05130766532623633</v>
       </c>
       <c r="Z3">
-        <v>0.2812693976499439</v>
+        <v>0.3735391038295949</v>
       </c>
       <c r="AA3">
-        <v>-0.1034724594478323</v>
+        <v>-0.07048780148277073</v>
       </c>
       <c r="AB3">
-        <v>0.04481703761767163</v>
+        <v>0.0691974671216551</v>
       </c>
       <c r="AC3">
-        <v>-0.148289497065504</v>
+        <v>-0.1396852686044258</v>
       </c>
       <c r="AD3">
-        <v>869.1</v>
+        <v>962.3</v>
       </c>
       <c r="AE3">
-        <v>1490.949326273092</v>
+        <v>1216.604433451619</v>
       </c>
       <c r="AF3">
-        <v>2360.049326273092</v>
+        <v>2178.904433451619</v>
       </c>
       <c r="AG3">
-        <v>2258.149326273091</v>
+        <v>2106.404433451619</v>
       </c>
       <c r="AH3">
-        <v>0.6381703706517157</v>
+        <v>0.5767189530706023</v>
       </c>
       <c r="AI3">
-        <v>0.8037358856306588</v>
+        <v>0.7735102432217611</v>
       </c>
       <c r="AJ3">
-        <v>0.6279179004013284</v>
+        <v>0.568437476606101</v>
       </c>
       <c r="AK3">
-        <v>0.7966800836204208</v>
+        <v>0.7675269751704956</v>
       </c>
       <c r="AL3">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="AM3">
-        <v>19.4</v>
+        <v>18.82</v>
       </c>
       <c r="AN3">
-        <v>9.158061116965227</v>
+        <v>7.785598705501617</v>
       </c>
       <c r="AO3">
-        <v>-1.79126213592233</v>
+        <v>-0.6305418719211823</v>
       </c>
       <c r="AP3">
-        <v>23.79504031899991</v>
+        <v>17.04210706676067</v>
       </c>
       <c r="AQ3">
-        <v>-1.902061855670103</v>
+        <v>-0.6801275239107333</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_hospitals_healthcare_facilities.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="swx_aevs" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,121 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0989</v>
-      </c>
-      <c r="E2">
-        <v>0.29</v>
+        <v>0.1</v>
       </c>
       <c r="G2">
-        <v>0.03138052907786227</v>
+        <v>0.06494522691705791</v>
       </c>
       <c r="H2">
-        <v>0.03138052907786227</v>
+        <v>0.06494522691705791</v>
       </c>
       <c r="I2">
-        <v>-0.1892694513123313</v>
+        <v>-0.1953776804337735</v>
       </c>
       <c r="J2">
-        <v>-0.1887026037170304</v>
+        <v>-0.09964056257663524</v>
       </c>
       <c r="K2">
-        <v>30.6</v>
+        <v>2.21</v>
       </c>
       <c r="L2">
-        <v>0.03277283924172646</v>
+        <v>0.002161580594679186</v>
       </c>
       <c r="M2">
-        <v>40.8</v>
+        <v>75.85899999999999</v>
       </c>
       <c r="N2">
-        <v>0.02551275637818909</v>
+        <v>0.04482862545798368</v>
       </c>
       <c r="O2">
-        <v>1.333333333333333</v>
+        <v>34.32533936651583</v>
       </c>
       <c r="P2">
-        <v>35.4</v>
+        <v>75.5</v>
       </c>
       <c r="Q2">
-        <v>0.02213606803401701</v>
+        <v>0.04461647559390143</v>
       </c>
       <c r="R2">
-        <v>1.156862745098039</v>
+        <v>34.16289592760181</v>
       </c>
       <c r="S2">
-        <v>5.399999999999999</v>
+        <v>0.3589999999999947</v>
       </c>
       <c r="T2">
-        <v>0.1323529411764706</v>
+        <v>0.004732464176959816</v>
       </c>
       <c r="U2">
-        <v>72.5</v>
+        <v>61</v>
       </c>
       <c r="V2">
-        <v>0.04533516758379189</v>
+        <v>0.03604774849308592</v>
       </c>
       <c r="W2">
-        <v>0.05932531989143079</v>
+        <v>0.004145563684111799</v>
       </c>
       <c r="X2">
-        <v>0.1106329852176671</v>
+        <v>0.09788391578188375</v>
       </c>
       <c r="Y2">
-        <v>-0.05130766532623633</v>
+        <v>-0.09373835209777195</v>
       </c>
       <c r="Z2">
-        <v>0.3735391038295949</v>
+        <v>0.362088292927996</v>
       </c>
       <c r="AA2">
-        <v>-0.07048780148277073</v>
+        <v>-0.03607868120975902</v>
       </c>
       <c r="AB2">
-        <v>0.0691974671216551</v>
+        <v>0.06231352645702556</v>
       </c>
       <c r="AC2">
-        <v>-0.1396852686044258</v>
+        <v>-0.09839220766678458</v>
       </c>
       <c r="AD2">
-        <v>962.3</v>
+        <v>1123.4</v>
       </c>
       <c r="AE2">
-        <v>1216.604433451619</v>
+        <v>1400.72070237745</v>
       </c>
       <c r="AF2">
-        <v>2178.904433451619</v>
+        <v>2524.12070237745</v>
       </c>
       <c r="AG2">
-        <v>2106.404433451619</v>
+        <v>2463.12070237745</v>
       </c>
       <c r="AH2">
-        <v>0.5767189530706023</v>
+        <v>0.5986548179207948</v>
       </c>
       <c r="AI2">
-        <v>0.7735102432217611</v>
+        <v>0.8185043638988145</v>
       </c>
       <c r="AJ2">
-        <v>0.568437476606101</v>
+        <v>0.5927630810705381</v>
       </c>
       <c r="AK2">
-        <v>0.7675269751704956</v>
+        <v>0.8148418132905483</v>
       </c>
       <c r="AL2">
-        <v>20.3</v>
+        <v>33</v>
       </c>
       <c r="AM2">
-        <v>18.82</v>
+        <v>32.033</v>
       </c>
       <c r="AN2">
-        <v>7.785598705501617</v>
+        <v>8.047277936962752</v>
       </c>
       <c r="AO2">
-        <v>-0.6305418719211823</v>
+        <v>0.0693939393939394</v>
       </c>
       <c r="AP2">
-        <v>17.04210706676067</v>
+        <v>17.64413110585566</v>
       </c>
       <c r="AQ2">
-        <v>-0.6801275239107333</v>
+        <v>0.07148877719851403</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +721,8890 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0989</v>
+        <v>0.1</v>
+      </c>
+      <c r="G3">
+        <v>0.06494522691705791</v>
+      </c>
+      <c r="H3">
+        <v>0.06494522691705791</v>
+      </c>
+      <c r="I3">
+        <v>-0.1953776804337735</v>
+      </c>
+      <c r="J3">
+        <v>-0.09964056257663524</v>
+      </c>
+      <c r="K3">
+        <v>2.21</v>
+      </c>
+      <c r="L3">
+        <v>0.002161580594679186</v>
+      </c>
+      <c r="M3">
+        <v>75.85899999999999</v>
+      </c>
+      <c r="N3">
+        <v>0.04482862545798368</v>
+      </c>
+      <c r="O3">
+        <v>34.32533936651583</v>
+      </c>
+      <c r="P3">
+        <v>75.5</v>
+      </c>
+      <c r="Q3">
+        <v>0.04461647559390143</v>
+      </c>
+      <c r="R3">
+        <v>34.16289592760181</v>
+      </c>
+      <c r="S3">
+        <v>0.3589999999999947</v>
+      </c>
+      <c r="T3">
+        <v>0.004732464176959816</v>
+      </c>
+      <c r="U3">
+        <v>61</v>
+      </c>
+      <c r="V3">
+        <v>0.03604774849308592</v>
+      </c>
+      <c r="W3">
+        <v>0.004145563684111799</v>
+      </c>
+      <c r="X3">
+        <v>0.09788391578188375</v>
+      </c>
+      <c r="Y3">
+        <v>-0.09373835209777195</v>
+      </c>
+      <c r="Z3">
+        <v>0.362088292927996</v>
+      </c>
+      <c r="AA3">
+        <v>-0.03607868120975902</v>
+      </c>
+      <c r="AB3">
+        <v>0.06231352645702556</v>
+      </c>
+      <c r="AC3">
+        <v>-0.09839220766678458</v>
+      </c>
+      <c r="AD3">
+        <v>1123.4</v>
+      </c>
+      <c r="AE3">
+        <v>1400.72070237745</v>
+      </c>
+      <c r="AF3">
+        <v>2524.12070237745</v>
+      </c>
+      <c r="AG3">
+        <v>2463.12070237745</v>
+      </c>
+      <c r="AH3">
+        <v>0.5986548179207948</v>
+      </c>
+      <c r="AI3">
+        <v>0.8185043638988145</v>
+      </c>
+      <c r="AJ3">
+        <v>0.5927630810705381</v>
+      </c>
+      <c r="AK3">
+        <v>0.8148418132905483</v>
+      </c>
+      <c r="AL3">
+        <v>33</v>
+      </c>
+      <c r="AM3">
+        <v>32.033</v>
+      </c>
+      <c r="AN3">
+        <v>8.047277936962752</v>
+      </c>
+      <c r="AO3">
+        <v>0.0693939393939394</v>
+      </c>
+      <c r="AP3">
+        <v>17.64413110585566</v>
+      </c>
+      <c r="AQ3">
+        <v>0.07148877719851403</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aevis Victoria SA (SWX:AEVS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SWX:AEVS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hospitals/Healthcare Facilities</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2.05757575757576</v>
+      </c>
+      <c r="F2">
+        <v>13.7621711357564</v>
+      </c>
+      <c r="G2">
+        <v>18.081093856572</v>
+      </c>
+      <c r="H2">
+        <v>2.4162296288696</v>
+      </c>
+      <c r="I2">
+        <v>0.598654817920795</v>
+      </c>
+      <c r="J2">
+        <v>0.08</v>
+      </c>
+      <c r="K2">
+        <v>1692.2</v>
+      </c>
+      <c r="L2">
+        <v>3535.79337946351</v>
+      </c>
+      <c r="M2">
+        <v>4155.32070237745</v>
+      </c>
+      <c r="N2">
+        <v>3812.09903565371</v>
+      </c>
+      <c r="O2">
+        <v>2524.12070237745</v>
+      </c>
+      <c r="P2">
+        <v>337.305656190196</v>
+      </c>
+      <c r="Q2">
+        <v>0.0623135264570256</v>
+      </c>
+      <c r="R2">
+        <v>0.06443056267923621</v>
+      </c>
+      <c r="S2">
+        <v>0.038466722</v>
+      </c>
+      <c r="T2">
+        <v>0.0381738</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0978839157818838</v>
+      </c>
+      <c r="X2">
+        <v>0.0667137594339524</v>
+      </c>
+      <c r="Y2">
+        <v>1.28443295178008</v>
+      </c>
+      <c r="Z2">
+        <v>0.606820857259834</v>
+      </c>
+      <c r="AA2">
+        <v>1123.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.045043</v>
+      </c>
+      <c r="AC2">
+        <v>2.057575757575757</v>
+      </c>
+      <c r="AD2">
+        <v>2524.12070237745</v>
+      </c>
+      <c r="AE2">
+        <v>33</v>
+      </c>
+      <c r="AF2">
+        <v>71.7</v>
+      </c>
+      <c r="AG2">
+        <v>139.6</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>1692.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.146</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>33</v>
+      </c>
+      <c r="AS2">
+        <v>1123.4</v>
+      </c>
+      <c r="AT2">
+        <v>61</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0647841535932048</v>
+      </c>
+      <c r="C2">
+        <v>3821.224204429335</v>
+      </c>
+      <c r="D2">
+        <v>3760.224204429335</v>
+      </c>
+      <c r="E2">
+        <v>-2524.12070237745</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>61</v>
+      </c>
+      <c r="H2">
+        <v>1692.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>279.2</v>
+      </c>
+      <c r="K2">
+        <v>71.7</v>
+      </c>
+      <c r="L2">
+        <v>207.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>207.5</v>
+      </c>
+      <c r="O2">
+        <v>30.295</v>
+      </c>
+      <c r="P2">
+        <v>177.205</v>
+      </c>
+      <c r="Q2">
+        <v>248.905</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.0647841535932048</v>
+      </c>
+      <c r="T2">
+        <v>0.5648729042001043</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.146</v>
+      </c>
+      <c r="W2">
+        <v>0.0381738</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.06473995472895872</v>
+      </c>
+      <c r="C3">
+        <v>3785.468010867341</v>
+      </c>
+      <c r="D3">
+        <v>3766.631217891116</v>
       </c>
       <c r="E3">
+        <v>-2481.957495353675</v>
+      </c>
+      <c r="F3">
+        <v>42.1632070237745</v>
+      </c>
+      <c r="G3">
+        <v>61</v>
+      </c>
+      <c r="H3">
+        <v>1692.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>279.2</v>
+      </c>
+      <c r="K3">
+        <v>71.7</v>
+      </c>
+      <c r="L3">
+        <v>207.5</v>
+      </c>
+      <c r="M3">
+        <v>1.88469535396272</v>
+      </c>
+      <c r="N3">
+        <v>205.6153046460373</v>
+      </c>
+      <c r="O3">
+        <v>30.01983447832144</v>
+      </c>
+      <c r="P3">
+        <v>175.5954701677159</v>
+      </c>
+      <c r="Q3">
+        <v>247.2954701677158</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.06500829972622092</v>
+      </c>
+      <c r="T3">
+        <v>0.569745646222194</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.146</v>
+      </c>
+      <c r="W3">
+        <v>0.0381738</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>110.0973690860515</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.06469575586471264</v>
+      </c>
+      <c r="C4">
+        <v>3749.733688280628</v>
+      </c>
+      <c r="D4">
+        <v>3773.060102328177</v>
+      </c>
+      <c r="E4">
+        <v>-2439.794288329901</v>
+      </c>
+      <c r="F4">
+        <v>84.32641404754899</v>
+      </c>
+      <c r="G4">
+        <v>61</v>
+      </c>
+      <c r="H4">
+        <v>1692.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>279.2</v>
+      </c>
+      <c r="K4">
+        <v>71.7</v>
+      </c>
+      <c r="L4">
+        <v>207.5</v>
+      </c>
+      <c r="M4">
+        <v>3.769390707925441</v>
+      </c>
+      <c r="N4">
+        <v>203.7306092920745</v>
+      </c>
+      <c r="O4">
+        <v>29.74466895664288</v>
+      </c>
+      <c r="P4">
+        <v>173.9859403354317</v>
+      </c>
+      <c r="Q4">
+        <v>245.6859403354317</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.06523702027011494</v>
+      </c>
+      <c r="T4">
+        <v>0.5747178319590204</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.146</v>
+      </c>
+      <c r="W4">
+        <v>0.0381738</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>55.04868454302572</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.06465155700046656</v>
+      </c>
+      <c r="C5">
+        <v>3714.021348848779</v>
+      </c>
+      <c r="D5">
+        <v>3779.510969920103</v>
+      </c>
+      <c r="E5">
+        <v>-2397.631081306126</v>
+      </c>
+      <c r="F5">
+        <v>126.4896210713235</v>
+      </c>
+      <c r="G5">
+        <v>61</v>
+      </c>
+      <c r="H5">
+        <v>1692.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>279.2</v>
+      </c>
+      <c r="K5">
+        <v>71.7</v>
+      </c>
+      <c r="L5">
+        <v>207.5</v>
+      </c>
+      <c r="M5">
+        <v>5.65408606188816</v>
+      </c>
+      <c r="N5">
+        <v>201.8459139381118</v>
+      </c>
+      <c r="O5">
+        <v>29.46950343496433</v>
+      </c>
+      <c r="P5">
+        <v>172.3764105031475</v>
+      </c>
+      <c r="Q5">
+        <v>244.0764105031475</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.06547045670151191</v>
+      </c>
+      <c r="T5">
+        <v>0.5797925369893895</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.146</v>
+      </c>
+      <c r="W5">
+        <v>0.0381738</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>36.69912302868382</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.06460735813622047</v>
+      </c>
+      <c r="C6">
+        <v>3678.331105519868</v>
+      </c>
+      <c r="D6">
+        <v>3785.983933614966</v>
+      </c>
+      <c r="E6">
+        <v>-2355.467874282352</v>
+      </c>
+      <c r="F6">
+        <v>168.652828095098</v>
+      </c>
+      <c r="G6">
+        <v>61</v>
+      </c>
+      <c r="H6">
+        <v>1692.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>279.2</v>
+      </c>
+      <c r="K6">
+        <v>71.7</v>
+      </c>
+      <c r="L6">
+        <v>207.5</v>
+      </c>
+      <c r="M6">
+        <v>7.538781415850881</v>
+      </c>
+      <c r="N6">
+        <v>199.9612185841491</v>
+      </c>
+      <c r="O6">
+        <v>29.19433791328577</v>
+      </c>
+      <c r="P6">
+        <v>170.7668806708633</v>
+      </c>
+      <c r="Q6">
+        <v>242.4668806708634</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.06570875639189633</v>
+      </c>
+      <c r="T6">
+        <v>0.5849729650412246</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.146</v>
+      </c>
+      <c r="W6">
+        <v>0.0381738</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>27.52434227151286</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.06456315927197441</v>
+      </c>
+      <c r="C7">
+        <v>3642.663072017054</v>
+      </c>
+      <c r="D7">
+        <v>3792.479107135927</v>
+      </c>
+      <c r="E7">
+        <v>-2313.304667258577</v>
+      </c>
+      <c r="F7">
+        <v>210.8160351188725</v>
+      </c>
+      <c r="G7">
+        <v>61</v>
+      </c>
+      <c r="H7">
+        <v>1692.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>279.2</v>
+      </c>
+      <c r="K7">
+        <v>71.7</v>
+      </c>
+      <c r="L7">
+        <v>207.5</v>
+      </c>
+      <c r="M7">
+        <v>9.4234767698136</v>
+      </c>
+      <c r="N7">
+        <v>198.0765232301864</v>
+      </c>
+      <c r="O7">
+        <v>28.91917239160722</v>
+      </c>
+      <c r="P7">
+        <v>169.1573508385792</v>
+      </c>
+      <c r="Q7">
+        <v>240.8573508385792</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.0659520729178678</v>
+      </c>
+      <c r="T7">
+        <v>0.5902624547362564</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.146</v>
+      </c>
+      <c r="W7">
+        <v>0.0381738</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>22.01947381721029</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.06451896040772831</v>
+      </c>
+      <c r="C8">
+        <v>3607.017362845258</v>
+      </c>
+      <c r="D8">
+        <v>3798.996604987904</v>
+      </c>
+      <c r="E8">
+        <v>-2271.141460234803</v>
+      </c>
+      <c r="F8">
+        <v>252.979242142647</v>
+      </c>
+      <c r="G8">
+        <v>61</v>
+      </c>
+      <c r="H8">
+        <v>1692.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>279.2</v>
+      </c>
+      <c r="K8">
+        <v>71.7</v>
+      </c>
+      <c r="L8">
+        <v>207.5</v>
+      </c>
+      <c r="M8">
+        <v>11.30817212377632</v>
+      </c>
+      <c r="N8">
+        <v>196.1918278762237</v>
+      </c>
+      <c r="O8">
+        <v>28.64400686992865</v>
+      </c>
+      <c r="P8">
+        <v>167.547821006295</v>
+      </c>
+      <c r="Q8">
+        <v>239.247821006295</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.06620056639120034</v>
+      </c>
+      <c r="T8">
+        <v>0.5956644867652249</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.146</v>
+      </c>
+      <c r="W8">
+        <v>0.0381738</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>18.34956151434191</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.06447476154348224</v>
+      </c>
+      <c r="C9">
+        <v>3571.394093297855</v>
+      </c>
+      <c r="D9">
+        <v>3805.536542464277</v>
+      </c>
+      <c r="E9">
+        <v>-2228.978253211028</v>
+      </c>
+      <c r="F9">
+        <v>295.1424491664215</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>1692.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>279.2</v>
+      </c>
+      <c r="K9">
+        <v>71.7</v>
+      </c>
+      <c r="L9">
+        <v>207.5</v>
+      </c>
+      <c r="M9">
+        <v>13.19286747773904</v>
+      </c>
+      <c r="N9">
+        <v>194.307132522261</v>
+      </c>
+      <c r="O9">
+        <v>28.3688413482501</v>
+      </c>
+      <c r="P9">
+        <v>165.9382911740109</v>
+      </c>
+      <c r="Q9">
+        <v>237.6382911740109</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.06645440381019596</v>
+      </c>
+      <c r="T9">
+        <v>0.6011826915259992</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.146</v>
+      </c>
+      <c r="W9">
+        <v>0.0381738</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>15.72819558372164</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.06443056267923618</v>
+      </c>
+      <c r="C10">
+        <v>3535.793379463513</v>
+      </c>
+      <c r="D10">
+        <v>3812.099035653709</v>
+      </c>
+      <c r="E10">
+        <v>-2186.815046187254</v>
+      </c>
+      <c r="F10">
+        <v>337.305656190196</v>
+      </c>
+      <c r="G10">
+        <v>61</v>
+      </c>
+      <c r="H10">
+        <v>1692.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>279.2</v>
+      </c>
+      <c r="K10">
+        <v>71.7</v>
+      </c>
+      <c r="L10">
+        <v>207.5</v>
+      </c>
+      <c r="M10">
+        <v>15.07756283170176</v>
+      </c>
+      <c r="N10">
+        <v>192.4224371682982</v>
+      </c>
+      <c r="O10">
+        <v>28.09367582657154</v>
+      </c>
+      <c r="P10">
+        <v>164.3287613417267</v>
+      </c>
+      <c r="Q10">
+        <v>236.0287613417267</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.06671375943395236</v>
+      </c>
+      <c r="T10">
+        <v>0.6068208572598337</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.146</v>
+      </c>
+      <c r="W10">
+        <v>0.0381738</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>13.76217113575643</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.06447090981499008</v>
+      </c>
+      <c r="C11">
+        <v>3487.638671616147</v>
+      </c>
+      <c r="D11">
+        <v>3806.107534830118</v>
+      </c>
+      <c r="E11">
+        <v>-2144.651839163479</v>
+      </c>
+      <c r="F11">
+        <v>379.4688632139705</v>
+      </c>
+      <c r="G11">
+        <v>61</v>
+      </c>
+      <c r="H11">
+        <v>1692.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>279.2</v>
+      </c>
+      <c r="K11">
+        <v>71.7</v>
+      </c>
+      <c r="L11">
+        <v>207.5</v>
+      </c>
+      <c r="M11">
+        <v>17.37967393519985</v>
+      </c>
+      <c r="N11">
+        <v>190.1203260648002</v>
+      </c>
+      <c r="O11">
+        <v>27.75756760546082</v>
+      </c>
+      <c r="P11">
+        <v>162.3627584593393</v>
+      </c>
+      <c r="Q11">
+        <v>234.0627584593394</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.06697881518130779</v>
+      </c>
+      <c r="T11">
+        <v>0.6125829387240822</v>
+      </c>
+      <c r="U11">
+        <v>0.0458</v>
+      </c>
+      <c r="V11">
+        <v>0.146</v>
+      </c>
+      <c r="W11">
+        <v>0.0391132</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>11.93923434775959</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.06443610495074401</v>
+      </c>
+      <c r="C12">
+        <v>3450.642827431238</v>
+      </c>
+      <c r="D12">
+        <v>3811.274897668983</v>
+      </c>
+      <c r="E12">
+        <v>-2102.488632139704</v>
+      </c>
+      <c r="F12">
+        <v>421.632070237745</v>
+      </c>
+      <c r="G12">
+        <v>61</v>
+      </c>
+      <c r="H12">
+        <v>1692.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>279.2</v>
+      </c>
+      <c r="K12">
+        <v>71.7</v>
+      </c>
+      <c r="L12">
+        <v>207.5</v>
+      </c>
+      <c r="M12">
+        <v>19.31074881688872</v>
+      </c>
+      <c r="N12">
+        <v>188.1892511831113</v>
+      </c>
+      <c r="O12">
+        <v>27.47563067273424</v>
+      </c>
+      <c r="P12">
+        <v>160.713620510377</v>
+      </c>
+      <c r="Q12">
+        <v>232.413620510377</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.06724976105638222</v>
+      </c>
+      <c r="T12">
+        <v>0.6184730664430919</v>
+      </c>
+      <c r="U12">
+        <v>0.0458</v>
+      </c>
+      <c r="V12">
+        <v>0.146</v>
+      </c>
+      <c r="W12">
+        <v>0.0391132</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>10.74531091298363</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.06460796808649794</v>
+      </c>
+      <c r="C13">
+        <v>3383.099177710918</v>
+      </c>
+      <c r="D13">
+        <v>3785.894454972438</v>
+      </c>
+      <c r="E13">
+        <v>-2060.32542511593</v>
+      </c>
+      <c r="F13">
+        <v>463.7952772615195</v>
+      </c>
+      <c r="G13">
+        <v>61</v>
+      </c>
+      <c r="H13">
+        <v>1692.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>279.2</v>
+      </c>
+      <c r="K13">
+        <v>71.7</v>
+      </c>
+      <c r="L13">
+        <v>207.5</v>
+      </c>
+      <c r="M13">
+        <v>22.26217330855293</v>
+      </c>
+      <c r="N13">
+        <v>185.2378266914471</v>
+      </c>
+      <c r="O13">
+        <v>27.04472269695127</v>
+      </c>
+      <c r="P13">
+        <v>158.1931039944958</v>
+      </c>
+      <c r="Q13">
+        <v>229.8931039944958</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.06752679560280667</v>
+      </c>
+      <c r="T13">
+        <v>0.6244955565827535</v>
+      </c>
+      <c r="U13">
+        <v>0.048</v>
+      </c>
+      <c r="V13">
+        <v>0.146</v>
+      </c>
+      <c r="W13">
+        <v>0.040992</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>9.320743178307765</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.06459195122225185</v>
+      </c>
+      <c r="C14">
+        <v>3343.287020323241</v>
+      </c>
+      <c r="D14">
+        <v>3788.245504608535</v>
+      </c>
+      <c r="E14">
+        <v>-2018.162218092156</v>
+      </c>
+      <c r="F14">
+        <v>505.9584842852939</v>
+      </c>
+      <c r="G14">
+        <v>61</v>
+      </c>
+      <c r="H14">
+        <v>1692.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>279.2</v>
+      </c>
+      <c r="K14">
+        <v>71.7</v>
+      </c>
+      <c r="L14">
+        <v>207.5</v>
+      </c>
+      <c r="M14">
+        <v>24.28600724569411</v>
+      </c>
+      <c r="N14">
+        <v>183.2139927543059</v>
+      </c>
+      <c r="O14">
+        <v>26.74924294212866</v>
+      </c>
+      <c r="P14">
+        <v>156.4647498121772</v>
+      </c>
+      <c r="Q14">
+        <v>228.1647498121772</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.06781012638892256</v>
+      </c>
+      <c r="T14">
+        <v>0.6306549214983164</v>
+      </c>
+      <c r="U14">
+        <v>0.048</v>
+      </c>
+      <c r="V14">
+        <v>0.146</v>
+      </c>
+      <c r="W14">
+        <v>0.040992</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.544014580115451</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.06457593435800577</v>
+      </c>
+      <c r="C15">
+        <v>3303.477784765075</v>
+      </c>
+      <c r="D15">
+        <v>3790.599476074144</v>
+      </c>
+      <c r="E15">
+        <v>-1975.999011068381</v>
+      </c>
+      <c r="F15">
+        <v>548.1216913090684</v>
+      </c>
+      <c r="G15">
+        <v>61</v>
+      </c>
+      <c r="H15">
+        <v>1692.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>279.2</v>
+      </c>
+      <c r="K15">
+        <v>71.7</v>
+      </c>
+      <c r="L15">
+        <v>207.5</v>
+      </c>
+      <c r="M15">
+        <v>26.30984118283529</v>
+      </c>
+      <c r="N15">
+        <v>181.1901588171647</v>
+      </c>
+      <c r="O15">
+        <v>26.45376318730605</v>
+      </c>
+      <c r="P15">
+        <v>154.7363956298587</v>
+      </c>
+      <c r="Q15">
+        <v>226.4363956298587</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.06809997052644341</v>
+      </c>
+      <c r="T15">
+        <v>0.6369558810096394</v>
+      </c>
+      <c r="U15">
+        <v>0.048</v>
+      </c>
+      <c r="V15">
+        <v>0.146</v>
+      </c>
+      <c r="W15">
+        <v>0.040992</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.886782689337341</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.06473925749375969</v>
+      </c>
+      <c r="C16">
+        <v>3237.447564856735</v>
+      </c>
+      <c r="D16">
+        <v>3766.732463189578</v>
+      </c>
+      <c r="E16">
+        <v>-1933.835804044606</v>
+      </c>
+      <c r="F16">
+        <v>590.284898332843</v>
+      </c>
+      <c r="G16">
+        <v>61</v>
+      </c>
+      <c r="H16">
+        <v>1692.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>279.2</v>
+      </c>
+      <c r="K16">
+        <v>71.7</v>
+      </c>
+      <c r="L16">
+        <v>207.5</v>
+      </c>
+      <c r="M16">
+        <v>29.21910246747573</v>
+      </c>
+      <c r="N16">
+        <v>178.2808975325243</v>
+      </c>
+      <c r="O16">
+        <v>26.02901103974854</v>
+      </c>
+      <c r="P16">
+        <v>152.2518864927757</v>
+      </c>
+      <c r="Q16">
+        <v>223.9518864927757</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.06839655522530197</v>
+      </c>
+      <c r="T16">
+        <v>0.6434033744630862</v>
+      </c>
+      <c r="U16">
+        <v>0.0495</v>
+      </c>
+      <c r="V16">
+        <v>0.146</v>
+      </c>
+      <c r="W16">
+        <v>0.042273</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>7.101518612044012</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.06473605062951361</v>
+      </c>
+      <c r="C17">
+        <v>3195.750095652234</v>
+      </c>
+      <c r="D17">
+        <v>3767.198201008852</v>
+      </c>
+      <c r="E17">
+        <v>-1891.672597020832</v>
+      </c>
+      <c r="F17">
+        <v>632.4481053566174</v>
+      </c>
+      <c r="G17">
+        <v>61</v>
+      </c>
+      <c r="H17">
+        <v>1692.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>279.2</v>
+      </c>
+      <c r="K17">
+        <v>71.7</v>
+      </c>
+      <c r="L17">
+        <v>207.5</v>
+      </c>
+      <c r="M17">
+        <v>31.30618121515256</v>
+      </c>
+      <c r="N17">
+        <v>176.1938187848475</v>
+      </c>
+      <c r="O17">
+        <v>25.72429754258773</v>
+      </c>
+      <c r="P17">
+        <v>150.4695212422597</v>
+      </c>
+      <c r="Q17">
+        <v>222.1695212422597</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.06870011838766307</v>
+      </c>
+      <c r="T17">
+        <v>0.6500025736448495</v>
+      </c>
+      <c r="U17">
+        <v>0.0495</v>
+      </c>
+      <c r="V17">
+        <v>0.146</v>
+      </c>
+      <c r="W17">
+        <v>0.042273</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.628084037907747</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.06473284376526754</v>
+      </c>
+      <c r="C18">
+        <v>3154.052741634324</v>
+      </c>
+      <c r="D18">
+        <v>3767.664054014716</v>
+      </c>
+      <c r="E18">
+        <v>-1849.509389997057</v>
+      </c>
+      <c r="F18">
+        <v>674.611312380392</v>
+      </c>
+      <c r="G18">
+        <v>61</v>
+      </c>
+      <c r="H18">
+        <v>1692.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>279.2</v>
+      </c>
+      <c r="K18">
+        <v>71.7</v>
+      </c>
+      <c r="L18">
+        <v>207.5</v>
+      </c>
+      <c r="M18">
+        <v>33.3932599628294</v>
+      </c>
+      <c r="N18">
+        <v>174.1067400371706</v>
+      </c>
+      <c r="O18">
+        <v>25.41958404542691</v>
+      </c>
+      <c r="P18">
+        <v>148.6871559917437</v>
+      </c>
+      <c r="Q18">
+        <v>220.3871559917437</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.06901090924436612</v>
+      </c>
+      <c r="T18">
+        <v>0.6567588966166547</v>
+      </c>
+      <c r="U18">
+        <v>0.0495</v>
+      </c>
+      <c r="V18">
+        <v>0.146</v>
+      </c>
+      <c r="W18">
+        <v>0.042273</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>6.21382878553851</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.06493288890102145</v>
+      </c>
+      <c r="C19">
+        <v>3083.048373190734</v>
+      </c>
+      <c r="D19">
+        <v>3738.822892594901</v>
+      </c>
+      <c r="E19">
+        <v>-1807.346182973283</v>
+      </c>
+      <c r="F19">
+        <v>716.7745194041664</v>
+      </c>
+      <c r="G19">
+        <v>61</v>
+      </c>
+      <c r="H19">
+        <v>1692.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>279.2</v>
+      </c>
+      <c r="K19">
+        <v>71.7</v>
+      </c>
+      <c r="L19">
+        <v>207.5</v>
+      </c>
+      <c r="M19">
+        <v>36.48382303767207</v>
+      </c>
+      <c r="N19">
+        <v>171.0161769623279</v>
+      </c>
+      <c r="O19">
+        <v>24.96836183649988</v>
+      </c>
+      <c r="P19">
+        <v>146.0478151258281</v>
+      </c>
+      <c r="Q19">
+        <v>217.7478151258281</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.06932918903737524</v>
+      </c>
+      <c r="T19">
+        <v>0.6636780225516358</v>
+      </c>
+      <c r="U19">
+        <v>0.0509</v>
+      </c>
+      <c r="V19">
+        <v>0.146</v>
+      </c>
+      <c r="W19">
+        <v>0.0434686</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.68745221096325</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.06494163803677538</v>
+      </c>
+      <c r="C20">
+        <v>3039.633849436109</v>
+      </c>
+      <c r="D20">
+        <v>3737.57157586405</v>
+      </c>
+      <c r="E20">
+        <v>-1765.182975949509</v>
+      </c>
+      <c r="F20">
+        <v>758.9377264279409</v>
+      </c>
+      <c r="G20">
+        <v>61</v>
+      </c>
+      <c r="H20">
+        <v>1692.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>279.2</v>
+      </c>
+      <c r="K20">
+        <v>71.7</v>
+      </c>
+      <c r="L20">
+        <v>207.5</v>
+      </c>
+      <c r="M20">
+        <v>38.62993027518219</v>
+      </c>
+      <c r="N20">
+        <v>168.8700697248178</v>
+      </c>
+      <c r="O20">
+        <v>24.6550301798234</v>
+      </c>
+      <c r="P20">
+        <v>144.2150395449944</v>
+      </c>
+      <c r="Q20">
+        <v>215.9150395449944</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.06965523175216509</v>
+      </c>
+      <c r="T20">
+        <v>0.6707659076557628</v>
+      </c>
+      <c r="U20">
+        <v>0.0509</v>
+      </c>
+      <c r="V20">
+        <v>0.146</v>
+      </c>
+      <c r="W20">
+        <v>0.0434686</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.371482643687515</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.06495038717252931</v>
+      </c>
+      <c r="C21">
+        <v>2996.220162987633</v>
+      </c>
+      <c r="D21">
+        <v>3736.321096439348</v>
+      </c>
+      <c r="E21">
+        <v>-1723.019768925734</v>
+      </c>
+      <c r="F21">
+        <v>801.1009334517154</v>
+      </c>
+      <c r="G21">
+        <v>61</v>
+      </c>
+      <c r="H21">
+        <v>1692.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>279.2</v>
+      </c>
+      <c r="K21">
+        <v>71.7</v>
+      </c>
+      <c r="L21">
+        <v>207.5</v>
+      </c>
+      <c r="M21">
+        <v>40.77603751269231</v>
+      </c>
+      <c r="N21">
+        <v>166.7239624873077</v>
+      </c>
+      <c r="O21">
+        <v>24.34169852314692</v>
+      </c>
+      <c r="P21">
+        <v>142.3822639641608</v>
+      </c>
+      <c r="Q21">
+        <v>214.0822639641607</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.06998932490435716</v>
+      </c>
+      <c r="T21">
+        <v>0.6780288022686338</v>
+      </c>
+      <c r="U21">
+        <v>0.0509</v>
+      </c>
+      <c r="V21">
+        <v>0.146</v>
+      </c>
+      <c r="W21">
+        <v>0.0434686</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.088773030861856</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.06495913630828322</v>
+      </c>
+      <c r="C22">
+        <v>2952.807313005173</v>
+      </c>
+      <c r="D22">
+        <v>3735.071453480663</v>
+      </c>
+      <c r="E22">
+        <v>-1680.85656190196</v>
+      </c>
+      <c r="F22">
+        <v>843.26414047549</v>
+      </c>
+      <c r="G22">
+        <v>61</v>
+      </c>
+      <c r="H22">
+        <v>1692.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>279.2</v>
+      </c>
+      <c r="K22">
+        <v>71.7</v>
+      </c>
+      <c r="L22">
+        <v>207.5</v>
+      </c>
+      <c r="M22">
+        <v>42.92214475020244</v>
+      </c>
+      <c r="N22">
+        <v>164.5778552497976</v>
+      </c>
+      <c r="O22">
+        <v>24.02836686647044</v>
+      </c>
+      <c r="P22">
+        <v>140.5494883833271</v>
+      </c>
+      <c r="Q22">
+        <v>212.2494883833271</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.07033177038535401</v>
+      </c>
+      <c r="T22">
+        <v>0.6854732692468265</v>
+      </c>
+      <c r="U22">
+        <v>0.0509</v>
+      </c>
+      <c r="V22">
+        <v>0.146</v>
+      </c>
+      <c r="W22">
+        <v>0.0434686</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.834334379318762</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.06496788544403714</v>
+      </c>
+      <c r="C23">
+        <v>2909.395298649717</v>
+      </c>
+      <c r="D23">
+        <v>3733.822646148981</v>
+      </c>
+      <c r="E23">
+        <v>-1638.693354878185</v>
+      </c>
+      <c r="F23">
+        <v>885.4273474992643</v>
+      </c>
+      <c r="G23">
+        <v>61</v>
+      </c>
+      <c r="H23">
+        <v>1692.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>279.2</v>
+      </c>
+      <c r="K23">
+        <v>71.7</v>
+      </c>
+      <c r="L23">
+        <v>207.5</v>
+      </c>
+      <c r="M23">
+        <v>45.06825198771256</v>
+      </c>
+      <c r="N23">
+        <v>162.4317480122874</v>
+      </c>
+      <c r="O23">
+        <v>23.71503520979396</v>
+      </c>
+      <c r="P23">
+        <v>138.7167128024935</v>
+      </c>
+      <c r="Q23">
+        <v>210.4167128024935</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.07068288537219891</v>
+      </c>
+      <c r="T23">
+        <v>0.6931062037434544</v>
+      </c>
+      <c r="U23">
+        <v>0.0509</v>
+      </c>
+      <c r="V23">
+        <v>0.146</v>
+      </c>
+      <c r="W23">
+        <v>0.0434686</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.604127980303584</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.06546512257979106</v>
+      </c>
+      <c r="C24">
+        <v>2797.605737108776</v>
+      </c>
+      <c r="D24">
+        <v>3664.196291631815</v>
+      </c>
+      <c r="E24">
+        <v>-1596.530147854411</v>
+      </c>
+      <c r="F24">
+        <v>927.5905545230389</v>
+      </c>
+      <c r="G24">
+        <v>61</v>
+      </c>
+      <c r="H24">
+        <v>1692.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>279.2</v>
+      </c>
+      <c r="K24">
+        <v>71.7</v>
+      </c>
+      <c r="L24">
+        <v>207.5</v>
+      </c>
+      <c r="M24">
+        <v>49.62609466698258</v>
+      </c>
+      <c r="N24">
+        <v>157.8739053330174</v>
+      </c>
+      <c r="O24">
+        <v>23.04959017862054</v>
+      </c>
+      <c r="P24">
+        <v>134.8243151543969</v>
+      </c>
+      <c r="Q24">
+        <v>206.5243151543969</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.07104300330742444</v>
+      </c>
+      <c r="T24">
+        <v>0.7009348545092269</v>
+      </c>
+      <c r="U24">
+        <v>0.0535</v>
+      </c>
+      <c r="V24">
+        <v>0.146</v>
+      </c>
+      <c r="W24">
+        <v>0.045689</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.181267967838998</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.06602640971554496</v>
+      </c>
+      <c r="C25">
+        <v>2679.903145242944</v>
+      </c>
+      <c r="D25">
+        <v>3588.656906789757</v>
+      </c>
+      <c r="E25">
+        <v>-1554.366940830636</v>
+      </c>
+      <c r="F25">
+        <v>969.7537615468134</v>
+      </c>
+      <c r="G25">
+        <v>61</v>
+      </c>
+      <c r="H25">
+        <v>1692.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>279.2</v>
+      </c>
+      <c r="K25">
+        <v>71.7</v>
+      </c>
+      <c r="L25">
+        <v>207.5</v>
+      </c>
+      <c r="M25">
+        <v>54.50016139893091</v>
+      </c>
+      <c r="N25">
+        <v>152.9998386010691</v>
+      </c>
+      <c r="O25">
+        <v>22.33797643575609</v>
+      </c>
+      <c r="P25">
+        <v>130.661862165313</v>
+      </c>
+      <c r="Q25">
+        <v>202.361862165313</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.07141247495525321</v>
+      </c>
+      <c r="T25">
+        <v>0.7089668468533309</v>
+      </c>
+      <c r="U25">
+        <v>0.0562</v>
+      </c>
+      <c r="V25">
+        <v>0.146</v>
+      </c>
+      <c r="W25">
+        <v>0.0479948</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.807328174335835</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.06608042085129891</v>
+      </c>
+      <c r="C26">
+        <v>2630.634936561626</v>
+      </c>
+      <c r="D26">
+        <v>3581.551905132214</v>
+      </c>
+      <c r="E26">
+        <v>-1512.203733806862</v>
+      </c>
+      <c r="F26">
+        <v>1011.916968570588</v>
+      </c>
+      <c r="G26">
+        <v>61</v>
+      </c>
+      <c r="H26">
+        <v>1692.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>279.2</v>
+      </c>
+      <c r="K26">
+        <v>71.7</v>
+      </c>
+      <c r="L26">
+        <v>207.5</v>
+      </c>
+      <c r="M26">
+        <v>56.86973363366704</v>
+      </c>
+      <c r="N26">
+        <v>150.630266366333</v>
+      </c>
+      <c r="O26">
+        <v>21.99201888948461</v>
+      </c>
+      <c r="P26">
+        <v>128.6382474768483</v>
+      </c>
+      <c r="Q26">
+        <v>200.3382474768483</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.07179166954118277</v>
+      </c>
+      <c r="T26">
+        <v>0.7172102074170166</v>
+      </c>
+      <c r="U26">
+        <v>0.0562</v>
+      </c>
+      <c r="V26">
+        <v>0.146</v>
+      </c>
+      <c r="W26">
+        <v>0.0479948</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.648689500405176</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.06613443198705282</v>
+      </c>
+      <c r="C27">
+        <v>2581.394805962143</v>
+      </c>
+      <c r="D27">
+        <v>3574.474981556505</v>
+      </c>
+      <c r="E27">
+        <v>-1470.040526783087</v>
+      </c>
+      <c r="F27">
+        <v>1054.080175594362</v>
+      </c>
+      <c r="G27">
+        <v>61</v>
+      </c>
+      <c r="H27">
+        <v>1692.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>279.2</v>
+      </c>
+      <c r="K27">
+        <v>71.7</v>
+      </c>
+      <c r="L27">
+        <v>207.5</v>
+      </c>
+      <c r="M27">
+        <v>59.23930586840316</v>
+      </c>
+      <c r="N27">
+        <v>148.2606941315968</v>
+      </c>
+      <c r="O27">
+        <v>21.64606134321314</v>
+      </c>
+      <c r="P27">
+        <v>126.6146327883837</v>
+      </c>
+      <c r="Q27">
+        <v>198.3146327883837</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.07218097598273709</v>
+      </c>
+      <c r="T27">
+        <v>0.7256733909290672</v>
+      </c>
+      <c r="U27">
+        <v>0.0562</v>
+      </c>
+      <c r="V27">
+        <v>0.146</v>
+      </c>
+      <c r="W27">
+        <v>0.0479948</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>3.502741920388968</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.06723203112280675</v>
+      </c>
+      <c r="C28">
+        <v>2401.241434479687</v>
+      </c>
+      <c r="D28">
+        <v>3436.484817097823</v>
+      </c>
+      <c r="E28">
+        <v>-1427.877319759313</v>
+      </c>
+      <c r="F28">
+        <v>1096.243382618137</v>
+      </c>
+      <c r="G28">
+        <v>61</v>
+      </c>
+      <c r="H28">
+        <v>1692.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>279.2</v>
+      </c>
+      <c r="K28">
+        <v>71.7</v>
+      </c>
+      <c r="L28">
+        <v>207.5</v>
+      </c>
+      <c r="M28">
+        <v>66.76122200144454</v>
+      </c>
+      <c r="N28">
+        <v>140.7387779985555</v>
+      </c>
+      <c r="O28">
+        <v>20.5478615877891</v>
+      </c>
+      <c r="P28">
+        <v>120.1909164107664</v>
+      </c>
+      <c r="Q28">
+        <v>191.8909164107664</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.07258080422000911</v>
+      </c>
+      <c r="T28">
+        <v>0.7343653091306328</v>
+      </c>
+      <c r="U28">
+        <v>0.0609</v>
+      </c>
+      <c r="V28">
+        <v>0.146</v>
+      </c>
+      <c r="W28">
+        <v>0.0520086</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>3.108091700231464</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.06947057425856065</v>
+      </c>
+      <c r="C29">
+        <v>2108.260638140979</v>
+      </c>
+      <c r="D29">
+        <v>3185.66722778289</v>
+      </c>
+      <c r="E29">
+        <v>-1385.714112735538</v>
+      </c>
+      <c r="F29">
+        <v>1138.406589641911</v>
+      </c>
+      <c r="G29">
+        <v>61</v>
+      </c>
+      <c r="H29">
+        <v>1692.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>279.2</v>
+      </c>
+      <c r="K29">
+        <v>71.7</v>
+      </c>
+      <c r="L29">
+        <v>207.5</v>
+      </c>
+      <c r="M29">
+        <v>79.91614259286217</v>
+      </c>
+      <c r="N29">
+        <v>127.5838574071378</v>
+      </c>
+      <c r="O29">
+        <v>18.62724318144212</v>
+      </c>
+      <c r="P29">
+        <v>108.9566142256957</v>
+      </c>
+      <c r="Q29">
+        <v>180.6566142256957</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.07299158665556255</v>
+      </c>
+      <c r="T29">
+        <v>0.7432953620774468</v>
+      </c>
+      <c r="U29">
+        <v>0.0702</v>
+      </c>
+      <c r="V29">
+        <v>0.146</v>
+      </c>
+      <c r="W29">
+        <v>0.0599508</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.596471667271553</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.0696441453943146</v>
+      </c>
+      <c r="C30">
+        <v>2048.170532129031</v>
+      </c>
+      <c r="D30">
+        <v>3167.740328794717</v>
+      </c>
+      <c r="E30">
+        <v>-1343.550905711764</v>
+      </c>
+      <c r="F30">
+        <v>1180.569796665686</v>
+      </c>
+      <c r="G30">
+        <v>61</v>
+      </c>
+      <c r="H30">
+        <v>1692.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>279.2</v>
+      </c>
+      <c r="K30">
+        <v>71.7</v>
+      </c>
+      <c r="L30">
+        <v>207.5</v>
+      </c>
+      <c r="M30">
+        <v>82.87599972593115</v>
+      </c>
+      <c r="N30">
+        <v>124.6240002740688</v>
+      </c>
+      <c r="O30">
+        <v>18.19510404001405</v>
+      </c>
+      <c r="P30">
+        <v>106.4288962340548</v>
+      </c>
+      <c r="Q30">
+        <v>178.1288962340548</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.07341377971432582</v>
+      </c>
+      <c r="T30">
+        <v>0.7524734720505613</v>
+      </c>
+      <c r="U30">
+        <v>0.0702</v>
+      </c>
+      <c r="V30">
+        <v>0.146</v>
+      </c>
+      <c r="W30">
+        <v>0.0599508</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.503740536297569</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
         <v>0.29</v>
       </c>
-      <c r="G3">
-        <v>0.03138052907786227</v>
-      </c>
-      <c r="H3">
-        <v>0.03138052907786227</v>
-      </c>
-      <c r="I3">
-        <v>-0.1892694513123313</v>
-      </c>
-      <c r="J3">
-        <v>-0.1887026037170304</v>
-      </c>
-      <c r="K3">
-        <v>30.6</v>
-      </c>
-      <c r="L3">
-        <v>0.03277283924172646</v>
-      </c>
-      <c r="M3">
-        <v>40.8</v>
-      </c>
-      <c r="N3">
-        <v>0.02551275637818909</v>
-      </c>
-      <c r="O3">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="P3">
-        <v>35.4</v>
-      </c>
-      <c r="Q3">
-        <v>0.02213606803401701</v>
-      </c>
-      <c r="R3">
-        <v>1.156862745098039</v>
-      </c>
-      <c r="S3">
-        <v>5.399999999999999</v>
-      </c>
-      <c r="T3">
-        <v>0.1323529411764706</v>
-      </c>
-      <c r="U3">
-        <v>72.5</v>
-      </c>
-      <c r="V3">
-        <v>0.04533516758379189</v>
-      </c>
-      <c r="W3">
-        <v>0.05932531989143079</v>
-      </c>
-      <c r="X3">
-        <v>0.1106329852176671</v>
-      </c>
-      <c r="Y3">
-        <v>-0.05130766532623633</v>
-      </c>
-      <c r="Z3">
-        <v>0.3735391038295949</v>
-      </c>
-      <c r="AA3">
-        <v>-0.07048780148277073</v>
-      </c>
-      <c r="AB3">
-        <v>0.0691974671216551</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1396852686044258</v>
-      </c>
-      <c r="AD3">
-        <v>962.3</v>
-      </c>
-      <c r="AE3">
-        <v>1216.604433451619</v>
-      </c>
-      <c r="AF3">
-        <v>2178.904433451619</v>
-      </c>
-      <c r="AG3">
-        <v>2106.404433451619</v>
-      </c>
-      <c r="AH3">
-        <v>0.5767189530706023</v>
-      </c>
-      <c r="AI3">
-        <v>0.7735102432217611</v>
-      </c>
-      <c r="AJ3">
-        <v>0.568437476606101</v>
-      </c>
-      <c r="AK3">
-        <v>0.7675269751704956</v>
-      </c>
-      <c r="AL3">
-        <v>20.3</v>
-      </c>
-      <c r="AM3">
-        <v>18.82</v>
-      </c>
-      <c r="AN3">
-        <v>7.785598705501617</v>
-      </c>
-      <c r="AO3">
-        <v>-0.6305418719211823</v>
-      </c>
-      <c r="AP3">
-        <v>17.04210706676067</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.6801275239107333</v>
+      <c r="B31">
+        <v>0.0709817185300685</v>
+      </c>
+      <c r="C31">
+        <v>1874.346103816493</v>
+      </c>
+      <c r="D31">
+        <v>3036.079107505953</v>
+      </c>
+      <c r="E31">
+        <v>-1301.387698687989</v>
+      </c>
+      <c r="F31">
+        <v>1222.73300368946</v>
+      </c>
+      <c r="G31">
+        <v>61</v>
+      </c>
+      <c r="H31">
+        <v>1692.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>279.2</v>
+      </c>
+      <c r="K31">
+        <v>71.7</v>
+      </c>
+      <c r="L31">
+        <v>207.5</v>
+      </c>
+      <c r="M31">
+        <v>91.58270197634056</v>
+      </c>
+      <c r="N31">
+        <v>115.9172980236594</v>
+      </c>
+      <c r="O31">
+        <v>16.92392551145428</v>
+      </c>
+      <c r="P31">
+        <v>98.99337251220516</v>
+      </c>
+      <c r="Q31">
+        <v>170.6933725122051</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.07384786553530776</v>
+      </c>
+      <c r="T31">
+        <v>0.7619101203327773</v>
+      </c>
+      <c r="U31">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V31">
+        <v>0.146</v>
+      </c>
+      <c r="W31">
+        <v>0.0639646</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.265711706710788</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.07119542766582243</v>
+      </c>
+      <c r="C32">
+        <v>1812.154210990549</v>
+      </c>
+      <c r="D32">
+        <v>3016.050421703784</v>
+      </c>
+      <c r="E32">
+        <v>-1259.224491664215</v>
+      </c>
+      <c r="F32">
+        <v>1264.896210713235</v>
+      </c>
+      <c r="G32">
+        <v>61</v>
+      </c>
+      <c r="H32">
+        <v>1692.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>279.2</v>
+      </c>
+      <c r="K32">
+        <v>71.7</v>
+      </c>
+      <c r="L32">
+        <v>207.5</v>
+      </c>
+      <c r="M32">
+        <v>94.74072618242127</v>
+      </c>
+      <c r="N32">
+        <v>112.7592738175787</v>
+      </c>
+      <c r="O32">
+        <v>16.46285397736649</v>
+      </c>
+      <c r="P32">
+        <v>96.29641984021224</v>
+      </c>
+      <c r="Q32">
+        <v>167.9964198402122</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.07429435380831775</v>
+      </c>
+      <c r="T32">
+        <v>0.7716163871373425</v>
+      </c>
+      <c r="U32">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V32">
+        <v>0.146</v>
+      </c>
+      <c r="W32">
+        <v>0.0639646</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.190187983153761</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.07140913680157635</v>
+      </c>
+      <c r="C33">
+        <v>1750.224840485214</v>
+      </c>
+      <c r="D33">
+        <v>2996.284258222223</v>
+      </c>
+      <c r="E33">
+        <v>-1217.06128464044</v>
+      </c>
+      <c r="F33">
+        <v>1307.059417737009</v>
+      </c>
+      <c r="G33">
+        <v>61</v>
+      </c>
+      <c r="H33">
+        <v>1692.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>279.2</v>
+      </c>
+      <c r="K33">
+        <v>71.7</v>
+      </c>
+      <c r="L33">
+        <v>207.5</v>
+      </c>
+      <c r="M33">
+        <v>97.89875038850198</v>
+      </c>
+      <c r="N33">
+        <v>109.601249611498</v>
+      </c>
+      <c r="O33">
+        <v>16.00178244327871</v>
+      </c>
+      <c r="P33">
+        <v>93.59946716821931</v>
+      </c>
+      <c r="Q33">
+        <v>165.2994671682193</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.07475378377040051</v>
+      </c>
+      <c r="T33">
+        <v>0.7816039950087067</v>
+      </c>
+      <c r="U33">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V33">
+        <v>0.146</v>
+      </c>
+      <c r="W33">
+        <v>0.0639646</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.119536757890737</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.07162284593733026</v>
+      </c>
+      <c r="C34">
+        <v>1688.552864461934</v>
+      </c>
+      <c r="D34">
+        <v>2976.775489222718</v>
+      </c>
+      <c r="E34">
+        <v>-1174.898077616666</v>
+      </c>
+      <c r="F34">
+        <v>1349.222624760784</v>
+      </c>
+      <c r="G34">
+        <v>61</v>
+      </c>
+      <c r="H34">
+        <v>1692.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>279.2</v>
+      </c>
+      <c r="K34">
+        <v>71.7</v>
+      </c>
+      <c r="L34">
+        <v>207.5</v>
+      </c>
+      <c r="M34">
+        <v>101.0567745945827</v>
+      </c>
+      <c r="N34">
+        <v>106.4432254054173</v>
+      </c>
+      <c r="O34">
+        <v>15.54071090919092</v>
+      </c>
+      <c r="P34">
+        <v>90.90251449622637</v>
+      </c>
+      <c r="Q34">
+        <v>162.6025144962264</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.07522672637842687</v>
+      </c>
+      <c r="T34">
+        <v>0.791885356052758</v>
+      </c>
+      <c r="U34">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V34">
+        <v>0.146</v>
+      </c>
+      <c r="W34">
+        <v>0.0639646</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.053301234206651</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.0764302210730842</v>
+      </c>
+      <c r="C35">
+        <v>1266.097539466869</v>
+      </c>
+      <c r="D35">
+        <v>2596.483371251428</v>
+      </c>
+      <c r="E35">
+        <v>-1132.734870592891</v>
+      </c>
+      <c r="F35">
+        <v>1391.385831784558</v>
+      </c>
+      <c r="G35">
+        <v>61</v>
+      </c>
+      <c r="H35">
+        <v>1692.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>279.2</v>
+      </c>
+      <c r="K35">
+        <v>71.7</v>
+      </c>
+      <c r="L35">
+        <v>207.5</v>
+      </c>
+      <c r="M35">
+        <v>126.8943878587517</v>
+      </c>
+      <c r="N35">
+        <v>80.60561214124827</v>
+      </c>
+      <c r="O35">
+        <v>11.76841937262225</v>
+      </c>
+      <c r="P35">
+        <v>68.83719276862602</v>
+      </c>
+      <c r="Q35">
+        <v>140.537192768626</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.07571378667624507</v>
+      </c>
+      <c r="T35">
+        <v>0.8024736233966318</v>
+      </c>
+      <c r="U35">
+        <v>0.0912</v>
+      </c>
+      <c r="V35">
+        <v>0.146</v>
+      </c>
+      <c r="W35">
+        <v>0.0778848</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>1.635218101457503</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.07678313220883812</v>
+      </c>
+      <c r="C36">
+        <v>1199.809731805202</v>
+      </c>
+      <c r="D36">
+        <v>2572.358770613535</v>
+      </c>
+      <c r="E36">
+        <v>-1090.571663569117</v>
+      </c>
+      <c r="F36">
+        <v>1433.549038808333</v>
+      </c>
+      <c r="G36">
+        <v>61</v>
+      </c>
+      <c r="H36">
+        <v>1692.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>279.2</v>
+      </c>
+      <c r="K36">
+        <v>71.7</v>
+      </c>
+      <c r="L36">
+        <v>207.5</v>
+      </c>
+      <c r="M36">
+        <v>130.73967233932</v>
+      </c>
+      <c r="N36">
+        <v>76.76032766068005</v>
+      </c>
+      <c r="O36">
+        <v>11.20700783845929</v>
+      </c>
+      <c r="P36">
+        <v>65.55331982222076</v>
+      </c>
+      <c r="Q36">
+        <v>137.2533198222208</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.07621560637702744</v>
+      </c>
+      <c r="T36">
+        <v>0.8133827473266836</v>
+      </c>
+      <c r="U36">
+        <v>0.0912</v>
+      </c>
+      <c r="V36">
+        <v>0.146</v>
+      </c>
+      <c r="W36">
+        <v>0.0778848</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>1.587123451414635</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.07713604334459202</v>
+      </c>
+      <c r="C37">
+        <v>1133.966093101411</v>
+      </c>
+      <c r="D37">
+        <v>2548.678338933519</v>
+      </c>
+      <c r="E37">
+        <v>-1048.408456545342</v>
+      </c>
+      <c r="F37">
+        <v>1475.712245832107</v>
+      </c>
+      <c r="G37">
+        <v>61</v>
+      </c>
+      <c r="H37">
+        <v>1692.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>279.2</v>
+      </c>
+      <c r="K37">
+        <v>71.7</v>
+      </c>
+      <c r="L37">
+        <v>207.5</v>
+      </c>
+      <c r="M37">
+        <v>134.5849568198882</v>
+      </c>
+      <c r="N37">
+        <v>72.91504318011181</v>
+      </c>
+      <c r="O37">
+        <v>10.64559630429632</v>
+      </c>
+      <c r="P37">
+        <v>62.26944687581549</v>
+      </c>
+      <c r="Q37">
+        <v>133.9694468758155</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.07673286668398774</v>
+      </c>
+      <c r="T37">
+        <v>0.8246275366084291</v>
+      </c>
+      <c r="U37">
+        <v>0.0912</v>
+      </c>
+      <c r="V37">
+        <v>0.146</v>
+      </c>
+      <c r="W37">
+        <v>0.0778848</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.541777067088503</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09881476531262867</v>
+      </c>
+      <c r="C38">
+        <v>171.1612938314909</v>
+      </c>
+      <c r="D38">
+        <v>1628.036746687373</v>
+      </c>
+      <c r="E38">
+        <v>-1006.245249521568</v>
+      </c>
+      <c r="F38">
+        <v>1517.875452855882</v>
+      </c>
+      <c r="G38">
+        <v>61</v>
+      </c>
+      <c r="H38">
+        <v>1692.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>279.2</v>
+      </c>
+      <c r="K38">
+        <v>71.7</v>
+      </c>
+      <c r="L38">
+        <v>207.5</v>
+      </c>
+      <c r="M38">
+        <v>237.6992959172311</v>
+      </c>
+      <c r="N38">
+        <v>-30.19929591723113</v>
+      </c>
+      <c r="O38">
+        <v>-4.409097203915744</v>
+      </c>
+      <c r="P38">
+        <v>-25.79019871331538</v>
+      </c>
+      <c r="Q38">
+        <v>45.90980128668462</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.07753740595925399</v>
+      </c>
+      <c r="T38">
+        <v>0.8421175208533477</v>
+      </c>
+      <c r="U38">
+        <v>0.1566</v>
+      </c>
+      <c r="V38">
+        <v>0.127450945460726</v>
+      </c>
+      <c r="W38">
+        <v>0.1366411819408503</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.8729516812378495</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09999276531262867</v>
+      </c>
+      <c r="C39">
+        <v>97.65733471390763</v>
+      </c>
+      <c r="D39">
+        <v>1596.695994593564</v>
+      </c>
+      <c r="E39">
+        <v>-964.0820424977933</v>
+      </c>
+      <c r="F39">
+        <v>1560.038659879656</v>
+      </c>
+      <c r="G39">
+        <v>61</v>
+      </c>
+      <c r="H39">
+        <v>1692.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>279.2</v>
+      </c>
+      <c r="K39">
+        <v>71.7</v>
+      </c>
+      <c r="L39">
+        <v>207.5</v>
+      </c>
+      <c r="M39">
+        <v>244.3020541371542</v>
+      </c>
+      <c r="N39">
+        <v>-36.80205413715419</v>
+      </c>
+      <c r="O39">
+        <v>-5.373099904024511</v>
+      </c>
+      <c r="P39">
+        <v>-31.42895423312968</v>
+      </c>
+      <c r="Q39">
+        <v>40.27104576687033</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.07815228541892469</v>
+      </c>
+      <c r="T39">
+        <v>0.8554844656287977</v>
+      </c>
+      <c r="U39">
+        <v>0.1566</v>
+      </c>
+      <c r="V39">
+        <v>0.1240063253131388</v>
+      </c>
+      <c r="W39">
+        <v>0.1371806094559625</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.8493583925557455</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1011707653126287</v>
+      </c>
+      <c r="C40">
+        <v>25.33724453817399</v>
+      </c>
+      <c r="D40">
+        <v>1566.539111441605</v>
+      </c>
+      <c r="E40">
+        <v>-921.9188354740188</v>
+      </c>
+      <c r="F40">
+        <v>1602.201866903431</v>
+      </c>
+      <c r="G40">
+        <v>61</v>
+      </c>
+      <c r="H40">
+        <v>1692.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>279.2</v>
+      </c>
+      <c r="K40">
+        <v>71.7</v>
+      </c>
+      <c r="L40">
+        <v>207.5</v>
+      </c>
+      <c r="M40">
+        <v>250.9048123570773</v>
+      </c>
+      <c r="N40">
+        <v>-43.40481235707728</v>
+      </c>
+      <c r="O40">
+        <v>-6.337102604133282</v>
+      </c>
+      <c r="P40">
+        <v>-37.067709752944</v>
+      </c>
+      <c r="Q40">
+        <v>34.63229024705601</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.0787869996998751</v>
+      </c>
+      <c r="T40">
+        <v>0.8692826021711976</v>
+      </c>
+      <c r="U40">
+        <v>0.1566</v>
+      </c>
+      <c r="V40">
+        <v>0.1207430009627931</v>
+      </c>
+      <c r="W40">
+        <v>0.1376916460492266</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.8270068559095417</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1023487653126287</v>
+      </c>
+      <c r="C41">
+        <v>-45.86481263791825</v>
+      </c>
+      <c r="D41">
+        <v>1537.500261289287</v>
+      </c>
+      <c r="E41">
+        <v>-879.7556284502443</v>
+      </c>
+      <c r="F41">
+        <v>1644.365073927205</v>
+      </c>
+      <c r="G41">
+        <v>61</v>
+      </c>
+      <c r="H41">
+        <v>1692.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>279.2</v>
+      </c>
+      <c r="K41">
+        <v>71.7</v>
+      </c>
+      <c r="L41">
+        <v>207.5</v>
+      </c>
+      <c r="M41">
+        <v>257.5075705770004</v>
+      </c>
+      <c r="N41">
+        <v>-50.00757057700037</v>
+      </c>
+      <c r="O41">
+        <v>-7.301105304242053</v>
+      </c>
+      <c r="P41">
+        <v>-42.70646527275832</v>
+      </c>
+      <c r="Q41">
+        <v>28.99353472724169</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.07944252428511894</v>
+      </c>
+      <c r="T41">
+        <v>0.8835331366330206</v>
+      </c>
+      <c r="U41">
+        <v>0.1566</v>
+      </c>
+      <c r="V41">
+        <v>0.1176470265791317</v>
+      </c>
+      <c r="W41">
+        <v>0.138176475637708</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8058015519118611</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1247048187574492</v>
+      </c>
+      <c r="C42">
+        <v>-488.1503703048954</v>
+      </c>
+      <c r="D42">
+        <v>1137.377910646085</v>
+      </c>
+      <c r="E42">
+        <v>-837.5924214264696</v>
+      </c>
+      <c r="F42">
+        <v>1686.52828095098</v>
+      </c>
+      <c r="G42">
+        <v>61</v>
+      </c>
+      <c r="H42">
+        <v>1692.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>279.2</v>
+      </c>
+      <c r="K42">
+        <v>71.7</v>
+      </c>
+      <c r="L42">
+        <v>207.5</v>
+      </c>
+      <c r="M42">
+        <v>352.1471050625646</v>
+      </c>
+      <c r="N42">
+        <v>-144.6471050625646</v>
+      </c>
+      <c r="O42">
+        <v>-21.11847733913443</v>
+      </c>
+      <c r="P42">
+        <v>-123.5286277234302</v>
+      </c>
+      <c r="Q42">
+        <v>-51.82862772343017</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.08061665543123853</v>
+      </c>
+      <c r="T42">
+        <v>0.9090577267660549</v>
+      </c>
+      <c r="U42">
+        <v>0.2088</v>
+      </c>
+      <c r="V42">
+        <v>0.08602938818599007</v>
+      </c>
+      <c r="W42">
+        <v>0.1908370637467653</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5892423848355484</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1264048187574492</v>
+      </c>
+      <c r="C43">
+        <v>-552.3847655980244</v>
+      </c>
+      <c r="D43">
+        <v>1115.30672237673</v>
+      </c>
+      <c r="E43">
+        <v>-795.4292144026952</v>
+      </c>
+      <c r="F43">
+        <v>1728.691487974754</v>
+      </c>
+      <c r="G43">
+        <v>61</v>
+      </c>
+      <c r="H43">
+        <v>1692.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>279.2</v>
+      </c>
+      <c r="K43">
+        <v>71.7</v>
+      </c>
+      <c r="L43">
+        <v>207.5</v>
+      </c>
+      <c r="M43">
+        <v>360.9507826891287</v>
+      </c>
+      <c r="N43">
+        <v>-153.4507826891287</v>
+      </c>
+      <c r="O43">
+        <v>-22.4038142726128</v>
+      </c>
+      <c r="P43">
+        <v>-131.0469684165159</v>
+      </c>
+      <c r="Q43">
+        <v>-59.34696841651594</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.08132541230295443</v>
+      </c>
+      <c r="T43">
+        <v>0.9244654848468354</v>
+      </c>
+      <c r="U43">
+        <v>0.2088</v>
+      </c>
+      <c r="V43">
+        <v>0.08393111042535616</v>
+      </c>
+      <c r="W43">
+        <v>0.1912751841431856</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5748706193517545</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1281048187574492</v>
+      </c>
+      <c r="C44">
+        <v>-615.778869839002</v>
+      </c>
+      <c r="D44">
+        <v>1094.075825159527</v>
+      </c>
+      <c r="E44">
+        <v>-753.2660073789209</v>
+      </c>
+      <c r="F44">
+        <v>1770.854694998529</v>
+      </c>
+      <c r="G44">
+        <v>61</v>
+      </c>
+      <c r="H44">
+        <v>1692.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>279.2</v>
+      </c>
+      <c r="K44">
+        <v>71.7</v>
+      </c>
+      <c r="L44">
+        <v>207.5</v>
+      </c>
+      <c r="M44">
+        <v>369.7544603156928</v>
+      </c>
+      <c r="N44">
+        <v>-162.2544603156928</v>
+      </c>
+      <c r="O44">
+        <v>-23.68915120609115</v>
+      </c>
+      <c r="P44">
+        <v>-138.5653091096017</v>
+      </c>
+      <c r="Q44">
+        <v>-66.86530910960168</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.08205860906679847</v>
+      </c>
+      <c r="T44">
+        <v>0.9404045449304016</v>
+      </c>
+      <c r="U44">
+        <v>0.2088</v>
+      </c>
+      <c r="V44">
+        <v>0.08193275065332388</v>
+      </c>
+      <c r="W44">
+        <v>0.191692441663586</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5611832236529033</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1298048187574492</v>
+      </c>
+      <c r="C45">
+        <v>-678.3797737690072</v>
+      </c>
+      <c r="D45">
+        <v>1073.638128253296</v>
+      </c>
+      <c r="E45">
+        <v>-711.1028003551464</v>
+      </c>
+      <c r="F45">
+        <v>1813.017902022303</v>
+      </c>
+      <c r="G45">
+        <v>61</v>
+      </c>
+      <c r="H45">
+        <v>1692.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>279.2</v>
+      </c>
+      <c r="K45">
+        <v>71.7</v>
+      </c>
+      <c r="L45">
+        <v>207.5</v>
+      </c>
+      <c r="M45">
+        <v>378.5581379422569</v>
+      </c>
+      <c r="N45">
+        <v>-171.0581379422569</v>
+      </c>
+      <c r="O45">
+        <v>-24.97448813956951</v>
+      </c>
+      <c r="P45">
+        <v>-146.0836498026874</v>
+      </c>
+      <c r="Q45">
+        <v>-74.3836498026874</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.08281753203288265</v>
+      </c>
+      <c r="T45">
+        <v>0.9569028702800577</v>
+      </c>
+      <c r="U45">
+        <v>0.2088</v>
+      </c>
+      <c r="V45">
+        <v>0.08002733784743263</v>
+      </c>
+      <c r="W45">
+        <v>0.1920902918574561</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.5481324510098126</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1315048187574492</v>
+      </c>
+      <c r="C46">
+        <v>-740.2311139717701</v>
+      </c>
+      <c r="D46">
+        <v>1053.949995074308</v>
+      </c>
+      <c r="E46">
+        <v>-668.9395933313717</v>
+      </c>
+      <c r="F46">
+        <v>1855.181109046078</v>
+      </c>
+      <c r="G46">
+        <v>61</v>
+      </c>
+      <c r="H46">
+        <v>1692.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>279.2</v>
+      </c>
+      <c r="K46">
+        <v>71.7</v>
+      </c>
+      <c r="L46">
+        <v>207.5</v>
+      </c>
+      <c r="M46">
+        <v>387.3618155688211</v>
+      </c>
+      <c r="N46">
+        <v>-179.8618155688211</v>
+      </c>
+      <c r="O46">
+        <v>-26.25982507304788</v>
+      </c>
+      <c r="P46">
+        <v>-153.6019904957732</v>
+      </c>
+      <c r="Q46">
+        <v>-81.90199049577323</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.0836035593906127</v>
+      </c>
+      <c r="T46">
+        <v>0.9739904215350589</v>
+      </c>
+      <c r="U46">
+        <v>0.2088</v>
+      </c>
+      <c r="V46">
+        <v>0.07820853471453641</v>
+      </c>
+      <c r="W46">
+        <v>0.1924700579516048</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.535674895305044</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1332048187574492</v>
+      </c>
+      <c r="C47">
+        <v>-801.3733838782318</v>
+      </c>
+      <c r="D47">
+        <v>1034.97093219162</v>
+      </c>
+      <c r="E47">
+        <v>-626.7763863075972</v>
+      </c>
+      <c r="F47">
+        <v>1897.344316069852</v>
+      </c>
+      <c r="G47">
+        <v>61</v>
+      </c>
+      <c r="H47">
+        <v>1692.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>279.2</v>
+      </c>
+      <c r="K47">
+        <v>71.7</v>
+      </c>
+      <c r="L47">
+        <v>207.5</v>
+      </c>
+      <c r="M47">
+        <v>396.1654931953852</v>
+      </c>
+      <c r="N47">
+        <v>-188.6654931953852</v>
+      </c>
+      <c r="O47">
+        <v>-27.54516200652623</v>
+      </c>
+      <c r="P47">
+        <v>-161.120331188859</v>
+      </c>
+      <c r="Q47">
+        <v>-89.42033118885895</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.08441816956135112</v>
+      </c>
+      <c r="T47">
+        <v>0.9916993382902417</v>
+      </c>
+      <c r="U47">
+        <v>0.2088</v>
+      </c>
+      <c r="V47">
+        <v>0.07647056727643563</v>
+      </c>
+      <c r="W47">
+        <v>0.1928329455526802</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5237710087427097</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1349048187574493</v>
+      </c>
+      <c r="C48">
+        <v>-861.8442117629988</v>
+      </c>
+      <c r="D48">
+        <v>1016.663311330628</v>
+      </c>
+      <c r="E48">
+        <v>-584.6131792838228</v>
+      </c>
+      <c r="F48">
+        <v>1939.507523093627</v>
+      </c>
+      <c r="G48">
+        <v>61</v>
+      </c>
+      <c r="H48">
+        <v>1692.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>279.2</v>
+      </c>
+      <c r="K48">
+        <v>71.7</v>
+      </c>
+      <c r="L48">
+        <v>207.5</v>
+      </c>
+      <c r="M48">
+        <v>404.9691708219493</v>
+      </c>
+      <c r="N48">
+        <v>-197.4691708219493</v>
+      </c>
+      <c r="O48">
+        <v>-28.8304989400046</v>
+      </c>
+      <c r="P48">
+        <v>-168.6386718819447</v>
+      </c>
+      <c r="Q48">
+        <v>-96.93867188194473</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.08526295047915392</v>
+      </c>
+      <c r="T48">
+        <v>1.010064140851172</v>
+      </c>
+      <c r="U48">
+        <v>0.2088</v>
+      </c>
+      <c r="V48">
+        <v>0.07480816363999135</v>
+      </c>
+      <c r="W48">
+        <v>0.1931800554319698</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5123846824656942</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1366048187574492</v>
+      </c>
+      <c r="C49">
+        <v>-921.6786097487261</v>
+      </c>
+      <c r="D49">
+        <v>998.9921203686752</v>
+      </c>
+      <c r="E49">
+        <v>-542.4499722600483</v>
+      </c>
+      <c r="F49">
+        <v>1981.670730117401</v>
+      </c>
+      <c r="G49">
+        <v>61</v>
+      </c>
+      <c r="H49">
+        <v>1692.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>279.2</v>
+      </c>
+      <c r="K49">
+        <v>71.7</v>
+      </c>
+      <c r="L49">
+        <v>207.5</v>
+      </c>
+      <c r="M49">
+        <v>413.7728484485134</v>
+      </c>
+      <c r="N49">
+        <v>-206.2728484485134</v>
+      </c>
+      <c r="O49">
+        <v>-30.11583587348295</v>
+      </c>
+      <c r="P49">
+        <v>-176.1570125750304</v>
+      </c>
+      <c r="Q49">
+        <v>-104.4570125750304</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.08613960992215683</v>
+      </c>
+      <c r="T49">
+        <v>1.029121954829496</v>
+      </c>
+      <c r="U49">
+        <v>0.2088</v>
+      </c>
+      <c r="V49">
+        <v>0.07321650058382133</v>
+      </c>
+      <c r="W49">
+        <v>0.1935123946780981</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5014828807111051</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1528171504577585</v>
+      </c>
+      <c r="C50">
+        <v>-1105.890548532488</v>
+      </c>
+      <c r="D50">
+        <v>856.9433886086882</v>
+      </c>
+      <c r="E50">
+        <v>-500.2867652362738</v>
+      </c>
+      <c r="F50">
+        <v>2023.833937141176</v>
+      </c>
+      <c r="G50">
+        <v>61</v>
+      </c>
+      <c r="H50">
+        <v>1692.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>279.2</v>
+      </c>
+      <c r="K50">
+        <v>71.7</v>
+      </c>
+      <c r="L50">
+        <v>207.5</v>
+      </c>
+      <c r="M50">
+        <v>483.2915441893128</v>
+      </c>
+      <c r="N50">
+        <v>-275.7915441893128</v>
+      </c>
+      <c r="O50">
+        <v>-40.26556545163967</v>
+      </c>
+      <c r="P50">
+        <v>-235.5259787376731</v>
+      </c>
+      <c r="Q50">
+        <v>-163.8259787376731</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.08726600953663917</v>
+      </c>
+      <c r="T50">
+        <v>1.053608902970417</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.06268473008526915</v>
+      </c>
+      <c r="W50">
+        <v>0.2238308864556378</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.4293474663374599</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1548171504577585</v>
+      </c>
+      <c r="C51">
+        <v>-1162.826457440897</v>
+      </c>
+      <c r="D51">
+        <v>842.1706867240528</v>
+      </c>
+      <c r="E51">
+        <v>-458.1235582124996</v>
+      </c>
+      <c r="F51">
+        <v>2065.99714416495</v>
+      </c>
+      <c r="G51">
+        <v>61</v>
+      </c>
+      <c r="H51">
+        <v>1692.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>279.2</v>
+      </c>
+      <c r="K51">
+        <v>71.7</v>
+      </c>
+      <c r="L51">
+        <v>207.5</v>
+      </c>
+      <c r="M51">
+        <v>493.3601180265901</v>
+      </c>
+      <c r="N51">
+        <v>-285.8601180265901</v>
+      </c>
+      <c r="O51">
+        <v>-41.73557723188215</v>
+      </c>
+      <c r="P51">
+        <v>-244.1245407947079</v>
+      </c>
+      <c r="Q51">
+        <v>-172.4245407947079</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.08821632344912231</v>
+      </c>
+      <c r="T51">
+        <v>1.074267901067876</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.06140544987944733</v>
+      </c>
+      <c r="W51">
+        <v>0.224136378568788</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4205852731468995</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1568171504577585</v>
+      </c>
+      <c r="C52">
+        <v>-1219.2616695666</v>
+      </c>
+      <c r="D52">
+        <v>827.8986816221251</v>
+      </c>
+      <c r="E52">
+        <v>-415.9603511887249</v>
+      </c>
+      <c r="F52">
+        <v>2108.160351188725</v>
+      </c>
+      <c r="G52">
+        <v>61</v>
+      </c>
+      <c r="H52">
+        <v>1692.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>279.2</v>
+      </c>
+      <c r="K52">
+        <v>71.7</v>
+      </c>
+      <c r="L52">
+        <v>207.5</v>
+      </c>
+      <c r="M52">
+        <v>503.4286918638675</v>
+      </c>
+      <c r="N52">
+        <v>-295.9286918638675</v>
+      </c>
+      <c r="O52">
+        <v>-43.20558901212465</v>
+      </c>
+      <c r="P52">
+        <v>-252.7231028517428</v>
+      </c>
+      <c r="Q52">
+        <v>-181.0231028517428</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.08920464991810476</v>
+      </c>
+      <c r="T52">
+        <v>1.095753259089234</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.06017734088185839</v>
+      </c>
+      <c r="W52">
+        <v>0.2244296509974122</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.4121735676839615</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1588171504577585</v>
+      </c>
+      <c r="C53">
+        <v>-1275.22121617125</v>
+      </c>
+      <c r="D53">
+        <v>814.1023420412499</v>
+      </c>
+      <c r="E53">
+        <v>-373.7971441649502</v>
+      </c>
+      <c r="F53">
+        <v>2150.323558212499</v>
+      </c>
+      <c r="G53">
+        <v>61</v>
+      </c>
+      <c r="H53">
+        <v>1692.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>279.2</v>
+      </c>
+      <c r="K53">
+        <v>71.7</v>
+      </c>
+      <c r="L53">
+        <v>207.5</v>
+      </c>
+      <c r="M53">
+        <v>513.4972657011449</v>
+      </c>
+      <c r="N53">
+        <v>-305.9972657011449</v>
+      </c>
+      <c r="O53">
+        <v>-44.67560079236715</v>
+      </c>
+      <c r="P53">
+        <v>-261.3216649087777</v>
+      </c>
+      <c r="Q53">
+        <v>-189.6216649087777</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.09023331624296402</v>
+      </c>
+      <c r="T53">
+        <v>1.118115570499218</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.05899739302142978</v>
+      </c>
+      <c r="W53">
+        <v>0.2247114225464826</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.4040917330234917</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1608171504577585</v>
+      </c>
+      <c r="C54">
+        <v>-1330.728487353007</v>
+      </c>
+      <c r="D54">
+        <v>800.7582778832672</v>
+      </c>
+      <c r="E54">
+        <v>-331.6339371411759</v>
+      </c>
+      <c r="F54">
+        <v>2192.486765236274</v>
+      </c>
+      <c r="G54">
+        <v>61</v>
+      </c>
+      <c r="H54">
+        <v>1692.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>279.2</v>
+      </c>
+      <c r="K54">
+        <v>71.7</v>
+      </c>
+      <c r="L54">
+        <v>207.5</v>
+      </c>
+      <c r="M54">
+        <v>523.5658395384222</v>
+      </c>
+      <c r="N54">
+        <v>-316.0658395384222</v>
+      </c>
+      <c r="O54">
+        <v>-46.14561257260964</v>
+      </c>
+      <c r="P54">
+        <v>-269.9202269658126</v>
+      </c>
+      <c r="Q54">
+        <v>-198.2202269658126</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.09130484366469245</v>
+      </c>
+      <c r="T54">
+        <v>1.141409644884618</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.05786282777101767</v>
+      </c>
+      <c r="W54">
+        <v>0.224982356728281</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3963207381576553</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1628171504577585</v>
+      </c>
+      <c r="C55">
+        <v>-1385.805364380125</v>
+      </c>
+      <c r="D55">
+        <v>787.8446078799233</v>
+      </c>
+      <c r="E55">
+        <v>-289.4707301174012</v>
+      </c>
+      <c r="F55">
+        <v>2234.649972260048</v>
+      </c>
+      <c r="G55">
+        <v>61</v>
+      </c>
+      <c r="H55">
+        <v>1692.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>279.2</v>
+      </c>
+      <c r="K55">
+        <v>71.7</v>
+      </c>
+      <c r="L55">
+        <v>207.5</v>
+      </c>
+      <c r="M55">
+        <v>533.6344133756995</v>
+      </c>
+      <c r="N55">
+        <v>-326.1344133756995</v>
+      </c>
+      <c r="O55">
+        <v>-47.61562435285213</v>
+      </c>
+      <c r="P55">
+        <v>-278.5187890228474</v>
+      </c>
+      <c r="Q55">
+        <v>-206.8187890228474</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.09242196799798377</v>
+      </c>
+      <c r="T55">
+        <v>1.165694956477908</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.05677107630363998</v>
+      </c>
+      <c r="W55">
+        <v>0.2252430669786908</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3888429883810958</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1648171504577585</v>
+      </c>
+      <c r="C56">
+        <v>-1440.472339423063</v>
+      </c>
+      <c r="D56">
+        <v>775.34083986076</v>
+      </c>
+      <c r="E56">
+        <v>-247.307523093627</v>
+      </c>
+      <c r="F56">
+        <v>2276.813179283823</v>
+      </c>
+      <c r="G56">
+        <v>61</v>
+      </c>
+      <c r="H56">
+        <v>1692.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>279.2</v>
+      </c>
+      <c r="K56">
+        <v>71.7</v>
+      </c>
+      <c r="L56">
+        <v>207.5</v>
+      </c>
+      <c r="M56">
+        <v>543.7029872129768</v>
+      </c>
+      <c r="N56">
+        <v>-336.2029872129768</v>
+      </c>
+      <c r="O56">
+        <v>-49.08563613309462</v>
+      </c>
+      <c r="P56">
+        <v>-287.1173510798822</v>
+      </c>
+      <c r="Q56">
+        <v>-215.4173510798822</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.09358766295446168</v>
+      </c>
+      <c r="T56">
+        <v>1.19103615118395</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0557197600757948</v>
+      </c>
+      <c r="W56">
+        <v>0.2254941212939002</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3816421922999644</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1668171504577585</v>
+      </c>
+      <c r="C57">
+        <v>-1494.748624063209</v>
+      </c>
+      <c r="D57">
+        <v>763.2277622443886</v>
+      </c>
+      <c r="E57">
+        <v>-205.1443160698523</v>
+      </c>
+      <c r="F57">
+        <v>2318.976386307597</v>
+      </c>
+      <c r="G57">
+        <v>61</v>
+      </c>
+      <c r="H57">
+        <v>1692.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>279.2</v>
+      </c>
+      <c r="K57">
+        <v>71.7</v>
+      </c>
+      <c r="L57">
+        <v>207.5</v>
+      </c>
+      <c r="M57">
+        <v>553.7715610502543</v>
+      </c>
+      <c r="N57">
+        <v>-346.2715610502543</v>
+      </c>
+      <c r="O57">
+        <v>-50.55564791333712</v>
+      </c>
+      <c r="P57">
+        <v>-295.7159131369172</v>
+      </c>
+      <c r="Q57">
+        <v>-224.0159131369172</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.09480516657567194</v>
+      </c>
+      <c r="T57">
+        <v>1.217503621210259</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.05470667352896216</v>
+      </c>
+      <c r="W57">
+        <v>0.2257360463612838</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3747032433490559</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1688171504577585</v>
+      </c>
+      <c r="C58">
+        <v>-1548.652247786738</v>
+      </c>
+      <c r="D58">
+        <v>751.4873455446339</v>
+      </c>
+      <c r="E58">
+        <v>-162.9811090460776</v>
+      </c>
+      <c r="F58">
+        <v>2361.139593331372</v>
+      </c>
+      <c r="G58">
+        <v>61</v>
+      </c>
+      <c r="H58">
+        <v>1692.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>279.2</v>
+      </c>
+      <c r="K58">
+        <v>71.7</v>
+      </c>
+      <c r="L58">
+        <v>207.5</v>
+      </c>
+      <c r="M58">
+        <v>563.8401348875317</v>
+      </c>
+      <c r="N58">
+        <v>-356.3401348875317</v>
+      </c>
+      <c r="O58">
+        <v>-52.02565969357963</v>
+      </c>
+      <c r="P58">
+        <v>-304.314475193952</v>
+      </c>
+      <c r="Q58">
+        <v>-232.614475193952</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.09607801127057358</v>
+      </c>
+      <c r="T58">
+        <v>1.245174158055947</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.0537297686445164</v>
+      </c>
+      <c r="W58">
+        <v>0.2259693312476895</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3680121140035371</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1708171504577585</v>
+      </c>
+      <c r="C59">
+        <v>-1602.200147525647</v>
+      </c>
+      <c r="D59">
+        <v>740.1026528294991</v>
+      </c>
+      <c r="E59">
+        <v>-120.8179020223033</v>
+      </c>
+      <c r="F59">
+        <v>2403.302800355146</v>
+      </c>
+      <c r="G59">
+        <v>61</v>
+      </c>
+      <c r="H59">
+        <v>1692.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>279.2</v>
+      </c>
+      <c r="K59">
+        <v>71.7</v>
+      </c>
+      <c r="L59">
+        <v>207.5</v>
+      </c>
+      <c r="M59">
+        <v>573.908708724809</v>
+      </c>
+      <c r="N59">
+        <v>-366.408708724809</v>
+      </c>
+      <c r="O59">
+        <v>-53.49567147382211</v>
+      </c>
+      <c r="P59">
+        <v>-312.9130372509869</v>
+      </c>
+      <c r="Q59">
+        <v>-241.2130372509869</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.09741005804430786</v>
+      </c>
+      <c r="T59">
+        <v>1.274131696615388</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.05278714112443717</v>
+      </c>
+      <c r="W59">
+        <v>0.2261944306994844</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.361555761126282</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1728171504577585</v>
+      </c>
+      <c r="C60">
+        <v>-1655.408249181213</v>
+      </c>
+      <c r="D60">
+        <v>729.057758197707</v>
+      </c>
+      <c r="E60">
+        <v>-78.65469499852907</v>
+      </c>
+      <c r="F60">
+        <v>2445.46600737892</v>
+      </c>
+      <c r="G60">
+        <v>61</v>
+      </c>
+      <c r="H60">
+        <v>1692.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>279.2</v>
+      </c>
+      <c r="K60">
+        <v>71.7</v>
+      </c>
+      <c r="L60">
+        <v>207.5</v>
+      </c>
+      <c r="M60">
+        <v>583.9772825620862</v>
+      </c>
+      <c r="N60">
+        <v>-376.4772825620862</v>
+      </c>
+      <c r="O60">
+        <v>-54.96568325406458</v>
+      </c>
+      <c r="P60">
+        <v>-321.5115993080216</v>
+      </c>
+      <c r="Q60">
+        <v>-249.8115993080216</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.09880553561679137</v>
+      </c>
+      <c r="T60">
+        <v>1.304468165582421</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.05187701800160206</v>
+      </c>
+      <c r="W60">
+        <v>0.2264117681012174</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3553220411068635</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1748171504577585</v>
+      </c>
+      <c r="C61">
+        <v>-1708.291541955117</v>
+      </c>
+      <c r="D61">
+        <v>718.3376724475779</v>
+      </c>
+      <c r="E61">
+        <v>-36.49148797475436</v>
+      </c>
+      <c r="F61">
+        <v>2487.629214402695</v>
+      </c>
+      <c r="G61">
+        <v>61</v>
+      </c>
+      <c r="H61">
+        <v>1692.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>279.2</v>
+      </c>
+      <c r="K61">
+        <v>71.7</v>
+      </c>
+      <c r="L61">
+        <v>207.5</v>
+      </c>
+      <c r="M61">
+        <v>594.0458563993636</v>
+      </c>
+      <c r="N61">
+        <v>-386.5458563993636</v>
+      </c>
+      <c r="O61">
+        <v>-56.43569503430709</v>
+      </c>
+      <c r="P61">
+        <v>-330.1101613650566</v>
+      </c>
+      <c r="Q61">
+        <v>-258.4101613650566</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1002690852659814</v>
+      </c>
+      <c r="T61">
+        <v>1.336284462303943</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.05099774651004948</v>
+      </c>
+      <c r="W61">
+        <v>0.2266217381334002</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3492996336304759</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1768171504577585</v>
+      </c>
+      <c r="C62">
+        <v>-1760.864146217787</v>
+      </c>
+      <c r="D62">
+        <v>707.9282752086825</v>
+      </c>
+      <c r="E62">
+        <v>5.671719049019885</v>
+      </c>
+      <c r="F62">
+        <v>2529.792421426469</v>
+      </c>
+      <c r="G62">
+        <v>61</v>
+      </c>
+      <c r="H62">
+        <v>1692.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>279.2</v>
+      </c>
+      <c r="K62">
+        <v>71.7</v>
+      </c>
+      <c r="L62">
+        <v>207.5</v>
+      </c>
+      <c r="M62">
+        <v>604.1144302366409</v>
+      </c>
+      <c r="N62">
+        <v>-396.6144302366409</v>
+      </c>
+      <c r="O62">
+        <v>-57.90570681454957</v>
+      </c>
+      <c r="P62">
+        <v>-338.7087234220913</v>
+      </c>
+      <c r="Q62">
+        <v>-267.0087234220914</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1018058123976309</v>
+      </c>
+      <c r="T62">
+        <v>1.369691573861542</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05014778406821532</v>
+      </c>
+      <c r="W62">
+        <v>0.2268247091645102</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.343477973069968</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1788171504577585</v>
+      </c>
+      <c r="C63">
+        <v>-1813.139375560174</v>
+      </c>
+      <c r="D63">
+        <v>697.8162528900704</v>
+      </c>
+      <c r="E63">
+        <v>47.83492607279459</v>
+      </c>
+      <c r="F63">
+        <v>2571.955628450244</v>
+      </c>
+      <c r="G63">
+        <v>61</v>
+      </c>
+      <c r="H63">
+        <v>1692.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>279.2</v>
+      </c>
+      <c r="K63">
+        <v>71.7</v>
+      </c>
+      <c r="L63">
+        <v>207.5</v>
+      </c>
+      <c r="M63">
+        <v>614.1830040739184</v>
+      </c>
+      <c r="N63">
+        <v>-406.6830040739184</v>
+      </c>
+      <c r="O63">
+        <v>-59.37571859479208</v>
+      </c>
+      <c r="P63">
+        <v>-347.3072854791263</v>
+      </c>
+      <c r="Q63">
+        <v>-275.6072854791263</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1034213460488522</v>
+      </c>
+      <c r="T63">
+        <v>1.404811870627223</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.0493256892474249</v>
+      </c>
+      <c r="W63">
+        <v>0.227021025407715</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3378471866261979</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1808171504577585</v>
+      </c>
+      <c r="C64">
+        <v>-1865.129793602347</v>
+      </c>
+      <c r="D64">
+        <v>687.9890418716708</v>
+      </c>
+      <c r="E64">
+        <v>89.99813309656884</v>
+      </c>
+      <c r="F64">
+        <v>2614.118835474018</v>
+      </c>
+      <c r="G64">
+        <v>61</v>
+      </c>
+      <c r="H64">
+        <v>1692.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>279.2</v>
+      </c>
+      <c r="K64">
+        <v>71.7</v>
+      </c>
+      <c r="L64">
+        <v>207.5</v>
+      </c>
+      <c r="M64">
+        <v>624.2515779111957</v>
+      </c>
+      <c r="N64">
+        <v>-416.7515779111957</v>
+      </c>
+      <c r="O64">
+        <v>-60.84573037503456</v>
+      </c>
+      <c r="P64">
+        <v>-355.9058475361611</v>
+      </c>
+      <c r="Q64">
+        <v>-284.2058475361611</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1051219077869799</v>
+      </c>
+      <c r="T64">
+        <v>1.441780604064781</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.04853011361440192</v>
+      </c>
+      <c r="W64">
+        <v>0.2272110088688808</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3323980384548076</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1828171504577585</v>
+      </c>
+      <c r="C65">
+        <v>-1916.847266068604</v>
+      </c>
+      <c r="D65">
+        <v>678.4347764291888</v>
+      </c>
+      <c r="E65">
+        <v>132.1613401203435</v>
+      </c>
+      <c r="F65">
+        <v>2656.282042497793</v>
+      </c>
+      <c r="G65">
+        <v>61</v>
+      </c>
+      <c r="H65">
+        <v>1692.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>279.2</v>
+      </c>
+      <c r="K65">
+        <v>71.7</v>
+      </c>
+      <c r="L65">
+        <v>207.5</v>
+      </c>
+      <c r="M65">
+        <v>634.320151748473</v>
+      </c>
+      <c r="N65">
+        <v>-426.820151748473</v>
+      </c>
+      <c r="O65">
+        <v>-62.31574215527705</v>
+      </c>
+      <c r="P65">
+        <v>-364.5044095931959</v>
+      </c>
+      <c r="Q65">
+        <v>-292.8044095931959</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1069143917812226</v>
+      </c>
+      <c r="T65">
+        <v>1.480747647417883</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04775979435068126</v>
+      </c>
+      <c r="W65">
+        <v>0.2273949611090573</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3271218791142552</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1848171504577585</v>
+      </c>
+      <c r="C66">
+        <v>-1968.303008582934</v>
+      </c>
+      <c r="D66">
+        <v>669.1422409386341</v>
+      </c>
+      <c r="E66">
+        <v>174.3245471441182</v>
+      </c>
+      <c r="F66">
+        <v>2698.445249521568</v>
+      </c>
+      <c r="G66">
+        <v>61</v>
+      </c>
+      <c r="H66">
+        <v>1692.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>279.2</v>
+      </c>
+      <c r="K66">
+        <v>71.7</v>
+      </c>
+      <c r="L66">
+        <v>207.5</v>
+      </c>
+      <c r="M66">
+        <v>644.3887255857504</v>
+      </c>
+      <c r="N66">
+        <v>-436.8887255857504</v>
+      </c>
+      <c r="O66">
+        <v>-63.78575393551956</v>
+      </c>
+      <c r="P66">
+        <v>-373.1029716502309</v>
+      </c>
+      <c r="Q66">
+        <v>-301.4029716502309</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1088064582195899</v>
+      </c>
+      <c r="T66">
+        <v>1.521879526512824</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.04701354756395185</v>
+      </c>
+      <c r="W66">
+        <v>0.2275731648417283</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3220105997530949</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1868171504577585</v>
+      </c>
+      <c r="C67">
+        <v>-2019.507630589624</v>
+      </c>
+      <c r="D67">
+        <v>660.1008259557182</v>
+      </c>
+      <c r="E67">
+        <v>216.4877541678925</v>
+      </c>
+      <c r="F67">
+        <v>2740.608456545342</v>
+      </c>
+      <c r="G67">
+        <v>61</v>
+      </c>
+      <c r="H67">
+        <v>1692.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>279.2</v>
+      </c>
+      <c r="K67">
+        <v>71.7</v>
+      </c>
+      <c r="L67">
+        <v>207.5</v>
+      </c>
+      <c r="M67">
+        <v>654.4572994230277</v>
+      </c>
+      <c r="N67">
+        <v>-446.9572994230277</v>
+      </c>
+      <c r="O67">
+        <v>-65.25576571576204</v>
+      </c>
+      <c r="P67">
+        <v>-381.7015337072657</v>
+      </c>
+      <c r="Q67">
+        <v>-310.0015337072657</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1108066427401496</v>
+      </c>
+      <c r="T67">
+        <v>1.565361798698905</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04629026221681414</v>
+      </c>
+      <c r="W67">
+        <v>0.2277458853826248</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3170565905261242</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1888171504577585</v>
+      </c>
+      <c r="C68">
+        <v>-2070.471175760624</v>
+      </c>
+      <c r="D68">
+        <v>651.3004878084931</v>
+      </c>
+      <c r="E68">
+        <v>258.6509611916672</v>
+      </c>
+      <c r="F68">
+        <v>2782.771663569117</v>
+      </c>
+      <c r="G68">
+        <v>61</v>
+      </c>
+      <c r="H68">
+        <v>1692.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>279.2</v>
+      </c>
+      <c r="K68">
+        <v>71.7</v>
+      </c>
+      <c r="L68">
+        <v>207.5</v>
+      </c>
+      <c r="M68">
+        <v>664.5258732603052</v>
+      </c>
+      <c r="N68">
+        <v>-457.0258732603052</v>
+      </c>
+      <c r="O68">
+        <v>-66.72577749600455</v>
+      </c>
+      <c r="P68">
+        <v>-390.3000957643006</v>
+      </c>
+      <c r="Q68">
+        <v>-318.6000957643006</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1129244851736835</v>
+      </c>
+      <c r="T68">
+        <v>1.611401851601814</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.04558889460746846</v>
+      </c>
+      <c r="W68">
+        <v>0.2279133719677365</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3122527027908799</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1908171504577585</v>
+      </c>
+      <c r="C69">
+        <v>-2121.203159213206</v>
+      </c>
+      <c r="D69">
+        <v>642.7317113796853</v>
+      </c>
+      <c r="E69">
+        <v>300.8141682154419</v>
+      </c>
+      <c r="F69">
+        <v>2824.934870592891</v>
+      </c>
+      <c r="G69">
+        <v>61</v>
+      </c>
+      <c r="H69">
+        <v>1692.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>279.2</v>
+      </c>
+      <c r="K69">
+        <v>71.7</v>
+      </c>
+      <c r="L69">
+        <v>207.5</v>
+      </c>
+      <c r="M69">
+        <v>674.5944470975825</v>
+      </c>
+      <c r="N69">
+        <v>-467.0944470975825</v>
+      </c>
+      <c r="O69">
+        <v>-68.19578927624704</v>
+      </c>
+      <c r="P69">
+        <v>-398.8986578213354</v>
+      </c>
+      <c r="Q69">
+        <v>-327.1986578213354</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1151706816940981</v>
+      </c>
+      <c r="T69">
+        <v>1.660232210741263</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04490846334467043</v>
+      </c>
+      <c r="W69">
+        <v>0.2280758589532927</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3075922146895235</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1928171504577585</v>
+      </c>
+      <c r="C70">
+        <v>-2171.71260182788</v>
+      </c>
+      <c r="D70">
+        <v>634.3854757887863</v>
+      </c>
+      <c r="E70">
+        <v>342.9773752392161</v>
+      </c>
+      <c r="F70">
+        <v>2867.098077616666</v>
+      </c>
+      <c r="G70">
+        <v>61</v>
+      </c>
+      <c r="H70">
+        <v>1692.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>279.2</v>
+      </c>
+      <c r="K70">
+        <v>71.7</v>
+      </c>
+      <c r="L70">
+        <v>207.5</v>
+      </c>
+      <c r="M70">
+        <v>684.6630209348598</v>
+      </c>
+      <c r="N70">
+        <v>-477.1630209348598</v>
+      </c>
+      <c r="O70">
+        <v>-69.66580105648953</v>
+      </c>
+      <c r="P70">
+        <v>-407.4972198783703</v>
+      </c>
+      <c r="Q70">
+        <v>-335.7972198783703</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1175572654970387</v>
+      </c>
+      <c r="T70">
+        <v>1.712114467326928</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.04424804476607233</v>
+      </c>
+      <c r="W70">
+        <v>0.2282335669098619</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3030687997676188</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1948171504577585</v>
+      </c>
+      <c r="C71">
+        <v>-2222.008061926749</v>
+      </c>
+      <c r="D71">
+        <v>626.2532227136918</v>
+      </c>
+      <c r="E71">
+        <v>385.1405822629908</v>
+      </c>
+      <c r="F71">
+        <v>2909.26128464044</v>
+      </c>
+      <c r="G71">
+        <v>61</v>
+      </c>
+      <c r="H71">
+        <v>1692.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>279.2</v>
+      </c>
+      <c r="K71">
+        <v>71.7</v>
+      </c>
+      <c r="L71">
+        <v>207.5</v>
+      </c>
+      <c r="M71">
+        <v>694.7315947721372</v>
+      </c>
+      <c r="N71">
+        <v>-487.2315947721372</v>
+      </c>
+      <c r="O71">
+        <v>-71.13581283673203</v>
+      </c>
+      <c r="P71">
+        <v>-416.0957819354052</v>
+      </c>
+      <c r="Q71">
+        <v>-344.3957819354052</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1200978224485561</v>
+      </c>
+      <c r="T71">
+        <v>1.767343966272958</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.04360676875496983</v>
+      </c>
+      <c r="W71">
+        <v>0.2283867036213132</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2986764983217112</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1968171504577585</v>
+      </c>
+      <c r="C72">
+        <v>-2272.097664546185</v>
+      </c>
+      <c r="D72">
+        <v>618.3268271180299</v>
+      </c>
+      <c r="E72">
+        <v>427.3037892867651</v>
+      </c>
+      <c r="F72">
+        <v>2951.424491664215</v>
+      </c>
+      <c r="G72">
+        <v>61</v>
+      </c>
+      <c r="H72">
+        <v>1692.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>279.2</v>
+      </c>
+      <c r="K72">
+        <v>71.7</v>
+      </c>
+      <c r="L72">
+        <v>207.5</v>
+      </c>
+      <c r="M72">
+        <v>704.8001686094145</v>
+      </c>
+      <c r="N72">
+        <v>-497.3001686094145</v>
+      </c>
+      <c r="O72">
+        <v>-72.60582461697452</v>
+      </c>
+      <c r="P72">
+        <v>-424.69434399244</v>
+      </c>
+      <c r="Q72">
+        <v>-352.99434399244</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1228077498635079</v>
+      </c>
+      <c r="T72">
+        <v>1.82625543181539</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.04298381491561313</v>
+      </c>
+      <c r="W72">
+        <v>0.2285354649981516</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2944096912028297</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1988171504577585</v>
+      </c>
+      <c r="C73">
+        <v>-2321.989128514283</v>
+      </c>
+      <c r="D73">
+        <v>610.5985701737063</v>
+      </c>
+      <c r="E73">
+        <v>469.4669963105393</v>
+      </c>
+      <c r="F73">
+        <v>2993.587698687989</v>
+      </c>
+      <c r="G73">
+        <v>61</v>
+      </c>
+      <c r="H73">
+        <v>1692.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>279.2</v>
+      </c>
+      <c r="K73">
+        <v>71.7</v>
+      </c>
+      <c r="L73">
+        <v>207.5</v>
+      </c>
+      <c r="M73">
+        <v>714.8687424466918</v>
+      </c>
+      <c r="N73">
+        <v>-507.3687424466918</v>
+      </c>
+      <c r="O73">
+        <v>-74.075836397217</v>
+      </c>
+      <c r="P73">
+        <v>-433.2929060494748</v>
+      </c>
+      <c r="Q73">
+        <v>-361.5929060494748</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1257045688243185</v>
+      </c>
+      <c r="T73">
+        <v>1.889229757050402</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04237840907173125</v>
+      </c>
+      <c r="W73">
+        <v>0.2286800359136706</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2902630758337758</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2008171504577585</v>
+      </c>
+      <c r="C74">
+        <v>-2371.689791522791</v>
+      </c>
+      <c r="D74">
+        <v>603.0611141889725</v>
+      </c>
+      <c r="E74">
+        <v>511.630203334314</v>
+      </c>
+      <c r="F74">
+        <v>3035.750905711764</v>
+      </c>
+      <c r="G74">
+        <v>61</v>
+      </c>
+      <c r="H74">
+        <v>1692.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>279.2</v>
+      </c>
+      <c r="K74">
+        <v>71.7</v>
+      </c>
+      <c r="L74">
+        <v>207.5</v>
+      </c>
+      <c r="M74">
+        <v>724.9373162839692</v>
+      </c>
+      <c r="N74">
+        <v>-517.4373162839692</v>
+      </c>
+      <c r="O74">
+        <v>-75.54584817745949</v>
+      </c>
+      <c r="P74">
+        <v>-441.8914681065096</v>
+      </c>
+      <c r="Q74">
+        <v>-370.1914681065097</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.128808303425187</v>
+      </c>
+      <c r="T74">
+        <v>1.956702248373631</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0417898200568461</v>
+      </c>
+      <c r="W74">
+        <v>0.2288205909704252</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2862316442249733</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2028171504577585</v>
+      </c>
+      <c r="C75">
+        <v>-2421.206633364704</v>
+      </c>
+      <c r="D75">
+        <v>595.7074793708346</v>
+      </c>
+      <c r="E75">
+        <v>553.7934103580883</v>
+      </c>
+      <c r="F75">
+        <v>3077.914112735538</v>
+      </c>
+      <c r="G75">
+        <v>61</v>
+      </c>
+      <c r="H75">
+        <v>1692.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>279.2</v>
+      </c>
+      <c r="K75">
+        <v>71.7</v>
+      </c>
+      <c r="L75">
+        <v>207.5</v>
+      </c>
+      <c r="M75">
+        <v>735.0058901212465</v>
+      </c>
+      <c r="N75">
+        <v>-527.5058901212465</v>
+      </c>
+      <c r="O75">
+        <v>-77.01585995770198</v>
+      </c>
+      <c r="P75">
+        <v>-450.4900301635445</v>
+      </c>
+      <c r="Q75">
+        <v>-378.7900301635445</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1321419442927866</v>
+      </c>
+      <c r="T75">
+        <v>2.029172702017099</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04121735676839615</v>
+      </c>
+      <c r="W75">
+        <v>0.228957295203707</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2823106627972339</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2048171504577585</v>
+      </c>
+      <c r="C76">
+        <v>-2470.546297492197</v>
+      </c>
+      <c r="D76">
+        <v>588.5310222671159</v>
+      </c>
+      <c r="E76">
+        <v>595.956617381863</v>
+      </c>
+      <c r="F76">
+        <v>3120.077319759313</v>
+      </c>
+      <c r="G76">
+        <v>61</v>
+      </c>
+      <c r="H76">
+        <v>1692.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>279.2</v>
+      </c>
+      <c r="K76">
+        <v>71.7</v>
+      </c>
+      <c r="L76">
+        <v>207.5</v>
+      </c>
+      <c r="M76">
+        <v>745.0744639585239</v>
+      </c>
+      <c r="N76">
+        <v>-537.5744639585239</v>
+      </c>
+      <c r="O76">
+        <v>-78.48587173794448</v>
+      </c>
+      <c r="P76">
+        <v>-459.0885922205794</v>
+      </c>
+      <c r="Q76">
+        <v>-387.3885922205794</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1357320190732783</v>
+      </c>
+      <c r="T76">
+        <v>2.107217805940834</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04066036546071512</v>
+      </c>
+      <c r="W76">
+        <v>0.2290903047279812</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2784956538405146</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2068171504577585</v>
+      </c>
+      <c r="C77">
+        <v>-2519.715111034873</v>
+      </c>
+      <c r="D77">
+        <v>581.5254157482138</v>
+      </c>
+      <c r="E77">
+        <v>638.1198244056377</v>
+      </c>
+      <c r="F77">
+        <v>3162.240526783087</v>
+      </c>
+      <c r="G77">
+        <v>61</v>
+      </c>
+      <c r="H77">
+        <v>1692.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>279.2</v>
+      </c>
+      <c r="K77">
+        <v>71.7</v>
+      </c>
+      <c r="L77">
+        <v>207.5</v>
+      </c>
+      <c r="M77">
+        <v>755.1430377958013</v>
+      </c>
+      <c r="N77">
+        <v>-547.6430377958013</v>
+      </c>
+      <c r="O77">
+        <v>-79.95588351818699</v>
+      </c>
+      <c r="P77">
+        <v>-467.6871542776144</v>
+      </c>
+      <c r="Q77">
+        <v>-395.9871542776144</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1396092998362095</v>
+      </c>
+      <c r="T77">
+        <v>2.191506518178467</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04011822725457224</v>
+      </c>
+      <c r="W77">
+        <v>0.2292197673316081</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2747823784559743</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2088171504577585</v>
+      </c>
+      <c r="C78">
+        <v>-2568.719103405097</v>
+      </c>
+      <c r="D78">
+        <v>574.684630401765</v>
+      </c>
+      <c r="E78">
+        <v>680.2830314294119</v>
+      </c>
+      <c r="F78">
+        <v>3204.403733806862</v>
+      </c>
+      <c r="G78">
+        <v>61</v>
+      </c>
+      <c r="H78">
+        <v>1692.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>279.2</v>
+      </c>
+      <c r="K78">
+        <v>71.7</v>
+      </c>
+      <c r="L78">
+        <v>207.5</v>
+      </c>
+      <c r="M78">
+        <v>765.2116116330785</v>
+      </c>
+      <c r="N78">
+        <v>-557.7116116330785</v>
+      </c>
+      <c r="O78">
+        <v>-81.42589529842945</v>
+      </c>
+      <c r="P78">
+        <v>-476.2857163346491</v>
+      </c>
+      <c r="Q78">
+        <v>-404.5857163346491</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1438096873293849</v>
+      </c>
+      <c r="T78">
+        <v>2.282819289769237</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03959035584332789</v>
+      </c>
+      <c r="W78">
+        <v>0.2293458230246133</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2711668208447116</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2108171504577585</v>
+      </c>
+      <c r="C79">
+        <v>-2617.564023605406</v>
+      </c>
+      <c r="D79">
+        <v>568.0029172252302</v>
+      </c>
+      <c r="E79">
+        <v>722.4462384531867</v>
+      </c>
+      <c r="F79">
+        <v>3246.566940830636</v>
+      </c>
+      <c r="G79">
+        <v>61</v>
+      </c>
+      <c r="H79">
+        <v>1692.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>279.2</v>
+      </c>
+      <c r="K79">
+        <v>71.7</v>
+      </c>
+      <c r="L79">
+        <v>207.5</v>
+      </c>
+      <c r="M79">
+        <v>775.2801854703559</v>
+      </c>
+      <c r="N79">
+        <v>-567.7801854703559</v>
+      </c>
+      <c r="O79">
+        <v>-82.89590707867197</v>
+      </c>
+      <c r="P79">
+        <v>-484.884278391684</v>
+      </c>
+      <c r="Q79">
+        <v>-413.184278391684</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1483753259089234</v>
+      </c>
+      <c r="T79">
+        <v>2.382072302367899</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03907619537783012</v>
+      </c>
+      <c r="W79">
+        <v>0.2294686045437742</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2676451738207543</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2128171504577585</v>
+      </c>
+      <c r="C80">
+        <v>-2666.255356342434</v>
+      </c>
+      <c r="D80">
+        <v>561.4747915119767</v>
+      </c>
+      <c r="E80">
+        <v>764.6094454769609</v>
+      </c>
+      <c r="F80">
+        <v>3288.73014785441</v>
+      </c>
+      <c r="G80">
+        <v>61</v>
+      </c>
+      <c r="H80">
+        <v>1692.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>279.2</v>
+      </c>
+      <c r="K80">
+        <v>71.7</v>
+      </c>
+      <c r="L80">
+        <v>207.5</v>
+      </c>
+      <c r="M80">
+        <v>785.3487593076333</v>
+      </c>
+      <c r="N80">
+        <v>-577.8487593076333</v>
+      </c>
+      <c r="O80">
+        <v>-84.36591885891445</v>
+      </c>
+      <c r="P80">
+        <v>-493.4828404487188</v>
+      </c>
+      <c r="Q80">
+        <v>-421.7828404487188</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1533560225411472</v>
+      </c>
+      <c r="T80">
+        <v>2.490348316111894</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03857521851401179</v>
+      </c>
+      <c r="W80">
+        <v>0.229588237818854</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2642138254384369</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2148171504577585</v>
+      </c>
+      <c r="C81">
+        <v>-2714.79833704226</v>
+      </c>
+      <c r="D81">
+        <v>555.0950178359254</v>
+      </c>
+      <c r="E81">
+        <v>806.7726525007356</v>
+      </c>
+      <c r="F81">
+        <v>3330.893354878185</v>
+      </c>
+      <c r="G81">
+        <v>61</v>
+      </c>
+      <c r="H81">
+        <v>1692.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>279.2</v>
+      </c>
+      <c r="K81">
+        <v>71.7</v>
+      </c>
+      <c r="L81">
+        <v>207.5</v>
+      </c>
+      <c r="M81">
+        <v>795.4173331449107</v>
+      </c>
+      <c r="N81">
+        <v>-587.9173331449107</v>
+      </c>
+      <c r="O81">
+        <v>-85.83593063915696</v>
+      </c>
+      <c r="P81">
+        <v>-502.0814025057537</v>
+      </c>
+      <c r="Q81">
+        <v>-430.3814025057537</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1588110712335827</v>
+      </c>
+      <c r="T81">
+        <v>2.608936331164842</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03808692460877112</v>
+      </c>
+      <c r="W81">
+        <v>0.2297048424034255</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2608693466354187</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2168171504577585</v>
+      </c>
+      <c r="C82">
+        <v>-2763.197965853582</v>
+      </c>
+      <c r="D82">
+        <v>548.858596048378</v>
+      </c>
+      <c r="E82">
+        <v>848.9358595245103</v>
+      </c>
+      <c r="F82">
+        <v>3373.05656190196</v>
+      </c>
+      <c r="G82">
+        <v>61</v>
+      </c>
+      <c r="H82">
+        <v>1692.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>279.2</v>
+      </c>
+      <c r="K82">
+        <v>71.7</v>
+      </c>
+      <c r="L82">
+        <v>207.5</v>
+      </c>
+      <c r="M82">
+        <v>805.4859069821881</v>
+      </c>
+      <c r="N82">
+        <v>-597.9859069821881</v>
+      </c>
+      <c r="O82">
+        <v>-87.30594241939946</v>
+      </c>
+      <c r="P82">
+        <v>-510.6799645627887</v>
+      </c>
+      <c r="Q82">
+        <v>-438.9799645627887</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.1648116247952619</v>
+      </c>
+      <c r="T82">
+        <v>2.739383147723085</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03761083805116149</v>
+      </c>
+      <c r="W82">
+        <v>0.2298185318733826</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2576084798024759</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2188171504577585</v>
+      </c>
+      <c r="C83">
+        <v>-2811.459020717439</v>
+      </c>
+      <c r="D83">
+        <v>542.7607482082952</v>
+      </c>
+      <c r="E83">
+        <v>891.0990665482846</v>
+      </c>
+      <c r="F83">
+        <v>3415.219768925734</v>
+      </c>
+      <c r="G83">
+        <v>61</v>
+      </c>
+      <c r="H83">
+        <v>1692.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>279.2</v>
+      </c>
+      <c r="K83">
+        <v>71.7</v>
+      </c>
+      <c r="L83">
+        <v>207.5</v>
+      </c>
+      <c r="M83">
+        <v>815.5544808194653</v>
+      </c>
+      <c r="N83">
+        <v>-608.0544808194653</v>
+      </c>
+      <c r="O83">
+        <v>-88.77595419964193</v>
+      </c>
+      <c r="P83">
+        <v>-519.2785266198234</v>
+      </c>
+      <c r="Q83">
+        <v>-447.5785266198234</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.1714438155739599</v>
+      </c>
+      <c r="T83">
+        <v>2.883561208129563</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03714650671719653</v>
+      </c>
+      <c r="W83">
+        <v>0.2299294141959335</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2544281281999763</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2208171504577585</v>
+      </c>
+      <c r="C84">
+        <v>-2859.586069575275</v>
+      </c>
+      <c r="D84">
+        <v>536.7969063742338</v>
+      </c>
+      <c r="E84">
+        <v>933.2622735720593</v>
+      </c>
+      <c r="F84">
+        <v>3457.382975949509</v>
+      </c>
+      <c r="G84">
+        <v>61</v>
+      </c>
+      <c r="H84">
+        <v>1692.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>279.2</v>
+      </c>
+      <c r="K84">
+        <v>71.7</v>
+      </c>
+      <c r="L84">
+        <v>207.5</v>
+      </c>
+      <c r="M84">
+        <v>825.6230546567427</v>
+      </c>
+      <c r="N84">
+        <v>-618.1230546567427</v>
+      </c>
+      <c r="O84">
+        <v>-90.24596597988443</v>
+      </c>
+      <c r="P84">
+        <v>-527.8770886768583</v>
+      </c>
+      <c r="Q84">
+        <v>-456.1770886768583</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.1788129164391799</v>
+      </c>
+      <c r="T84">
+        <v>3.04375905302565</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03669350053771852</v>
+      </c>
+      <c r="W84">
+        <v>0.2300375920715928</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.251325346148757</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2228171504577585</v>
+      </c>
+      <c r="C85">
+        <v>-2907.583481780891</v>
+      </c>
+      <c r="D85">
+        <v>530.9627011923917</v>
+      </c>
+      <c r="E85">
+        <v>975.4254805958335</v>
+      </c>
+      <c r="F85">
+        <v>3499.546182973283</v>
+      </c>
+      <c r="G85">
+        <v>61</v>
+      </c>
+      <c r="H85">
+        <v>1692.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>279.2</v>
+      </c>
+      <c r="K85">
+        <v>71.7</v>
+      </c>
+      <c r="L85">
+        <v>207.5</v>
+      </c>
+      <c r="M85">
+        <v>835.6916284940201</v>
+      </c>
+      <c r="N85">
+        <v>-628.1916284940201</v>
+      </c>
+      <c r="O85">
+        <v>-91.71597776012692</v>
+      </c>
+      <c r="P85">
+        <v>-536.4756507338932</v>
+      </c>
+      <c r="Q85">
+        <v>-464.7756507338932</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.1870489703473669</v>
+      </c>
+      <c r="T85">
+        <v>3.222803703203629</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0362514101697942</v>
+      </c>
+      <c r="W85">
+        <v>0.2301431632514532</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2482973299300973</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2248171504577585</v>
+      </c>
+      <c r="C86">
+        <v>-2955.455438776222</v>
+      </c>
+      <c r="D86">
+        <v>525.2539512208349</v>
+      </c>
+      <c r="E86">
+        <v>1017.588687619608</v>
+      </c>
+      <c r="F86">
+        <v>3541.709389997057</v>
+      </c>
+      <c r="G86">
+        <v>61</v>
+      </c>
+      <c r="H86">
+        <v>1692.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>279.2</v>
+      </c>
+      <c r="K86">
+        <v>71.7</v>
+      </c>
+      <c r="L86">
+        <v>207.5</v>
+      </c>
+      <c r="M86">
+        <v>845.7602023312974</v>
+      </c>
+      <c r="N86">
+        <v>-638.2602023312974</v>
+      </c>
+      <c r="O86">
+        <v>-93.18598954036941</v>
+      </c>
+      <c r="P86">
+        <v>-545.074212790928</v>
+      </c>
+      <c r="Q86">
+        <v>-473.374212790928</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.1963145309940773</v>
+      </c>
+      <c r="T86">
+        <v>3.424228934653855</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03581984576301094</v>
+      </c>
+      <c r="W86">
+        <v>0.230246220831793</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2453414093356914</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2268171504577585</v>
+      </c>
+      <c r="C87">
+        <v>-3003.205944085734</v>
+      </c>
+      <c r="D87">
+        <v>519.6666529350985</v>
+      </c>
+      <c r="E87">
+        <v>1059.751894643382</v>
+      </c>
+      <c r="F87">
+        <v>3583.872597020832</v>
+      </c>
+      <c r="G87">
+        <v>61</v>
+      </c>
+      <c r="H87">
+        <v>1692.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>279.2</v>
+      </c>
+      <c r="K87">
+        <v>71.7</v>
+      </c>
+      <c r="L87">
+        <v>207.5</v>
+      </c>
+      <c r="M87">
+        <v>855.8287761685747</v>
+      </c>
+      <c r="N87">
+        <v>-648.3287761685747</v>
+      </c>
+      <c r="O87">
+        <v>-94.65600132061189</v>
+      </c>
+      <c r="P87">
+        <v>-553.6727748479627</v>
+      </c>
+      <c r="Q87">
+        <v>-481.9727748479627</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2068154997270158</v>
+      </c>
+      <c r="T87">
+        <v>3.652510863630778</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03539843581285787</v>
+      </c>
+      <c r="W87">
+        <v>0.2303468535278896</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.242455039814095</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2288171504577585</v>
+      </c>
+      <c r="C88">
+        <v>-3050.838832679653</v>
+      </c>
+      <c r="D88">
+        <v>514.1969713649538</v>
+      </c>
+      <c r="E88">
+        <v>1101.915101667157</v>
+      </c>
+      <c r="F88">
+        <v>3626.035804044606</v>
+      </c>
+      <c r="G88">
+        <v>61</v>
+      </c>
+      <c r="H88">
+        <v>1692.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>279.2</v>
+      </c>
+      <c r="K88">
+        <v>71.7</v>
+      </c>
+      <c r="L88">
+        <v>207.5</v>
+      </c>
+      <c r="M88">
+        <v>865.897350005852</v>
+      </c>
+      <c r="N88">
+        <v>-658.397350005852</v>
+      </c>
+      <c r="O88">
+        <v>-96.12601310085438</v>
+      </c>
+      <c r="P88">
+        <v>-562.2713369049976</v>
+      </c>
+      <c r="Q88">
+        <v>-490.5713369049976</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2188166068503741</v>
+      </c>
+      <c r="T88">
+        <v>3.913404496747262</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03498682609410372</v>
+      </c>
+      <c r="W88">
+        <v>0.230445145928728</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2396357951650939</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2308171504577585</v>
+      </c>
+      <c r="C89">
+        <v>-3098.357779752054</v>
+      </c>
+      <c r="D89">
+        <v>508.841231316327</v>
+      </c>
+      <c r="E89">
+        <v>1144.078308690931</v>
+      </c>
+      <c r="F89">
+        <v>3668.199011068381</v>
+      </c>
+      <c r="G89">
+        <v>61</v>
+      </c>
+      <c r="H89">
+        <v>1692.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>279.2</v>
+      </c>
+      <c r="K89">
+        <v>71.7</v>
+      </c>
+      <c r="L89">
+        <v>207.5</v>
+      </c>
+      <c r="M89">
+        <v>875.9659238431294</v>
+      </c>
+      <c r="N89">
+        <v>-668.4659238431294</v>
+      </c>
+      <c r="O89">
+        <v>-97.59602488109689</v>
+      </c>
+      <c r="P89">
+        <v>-570.8698989620325</v>
+      </c>
+      <c r="Q89">
+        <v>-499.1698989620325</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2326640381465567</v>
+      </c>
+      <c r="T89">
+        <v>4.214435611881667</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.0345846786677347</v>
+      </c>
+      <c r="W89">
+        <v>0.230541178734145</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2368813607379089</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2328171504577585</v>
+      </c>
+      <c r="C90">
+        <v>-3145.766308956015</v>
+      </c>
+      <c r="D90">
+        <v>503.5959091361404</v>
+      </c>
+      <c r="E90">
+        <v>1186.241515714706</v>
+      </c>
+      <c r="F90">
+        <v>3710.362218092156</v>
+      </c>
+      <c r="G90">
+        <v>61</v>
+      </c>
+      <c r="H90">
+        <v>1692.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>279.2</v>
+      </c>
+      <c r="K90">
+        <v>71.7</v>
+      </c>
+      <c r="L90">
+        <v>207.5</v>
+      </c>
+      <c r="M90">
+        <v>886.0344976804068</v>
+      </c>
+      <c r="N90">
+        <v>-678.5344976804068</v>
+      </c>
+      <c r="O90">
+        <v>-99.0660366613394</v>
+      </c>
+      <c r="P90">
+        <v>-579.4684610190675</v>
+      </c>
+      <c r="Q90">
+        <v>-507.7684610190675</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.2488193746587698</v>
+      </c>
+      <c r="T90">
+        <v>4.565638579538474</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03419167095560135</v>
+      </c>
+      <c r="W90">
+        <v>0.2306350289758024</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.23418952709316</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2348171504577585</v>
+      </c>
+      <c r="C91">
+        <v>-3193.067800134621</v>
+      </c>
+      <c r="D91">
+        <v>498.4576249813088</v>
+      </c>
+      <c r="E91">
+        <v>1228.40472273848</v>
+      </c>
+      <c r="F91">
+        <v>3752.52542511593</v>
+      </c>
+      <c r="G91">
+        <v>61</v>
+      </c>
+      <c r="H91">
+        <v>1692.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>279.2</v>
+      </c>
+      <c r="K91">
+        <v>71.7</v>
+      </c>
+      <c r="L91">
+        <v>207.5</v>
+      </c>
+      <c r="M91">
+        <v>896.1030715176842</v>
+      </c>
+      <c r="N91">
+        <v>-688.6030715176842</v>
+      </c>
+      <c r="O91">
+        <v>-100.5360484415819</v>
+      </c>
+      <c r="P91">
+        <v>-588.0670230761023</v>
+      </c>
+      <c r="Q91">
+        <v>-516.3670230761022</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.2679120450822943</v>
+      </c>
+      <c r="T91">
+        <v>4.980696632223789</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03380749487744852</v>
+      </c>
+      <c r="W91">
+        <v>0.2307267702232653</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2315581840921133</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2368171504577585</v>
+      </c>
+      <c r="C92">
+        <v>-3240.265496583469</v>
+      </c>
+      <c r="D92">
+        <v>493.4231355562361</v>
+      </c>
+      <c r="E92">
+        <v>1270.567929762255</v>
+      </c>
+      <c r="F92">
+        <v>3794.688632139705</v>
+      </c>
+      <c r="G92">
+        <v>61</v>
+      </c>
+      <c r="H92">
+        <v>1692.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>279.2</v>
+      </c>
+      <c r="K92">
+        <v>71.7</v>
+      </c>
+      <c r="L92">
+        <v>207.5</v>
+      </c>
+      <c r="M92">
+        <v>906.1716453549615</v>
+      </c>
+      <c r="N92">
+        <v>-698.6716453549615</v>
+      </c>
+      <c r="O92">
+        <v>-102.0060602218244</v>
+      </c>
+      <c r="P92">
+        <v>-596.6655851331371</v>
+      </c>
+      <c r="Q92">
+        <v>-524.9655851331371</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.2908232495905238</v>
+      </c>
+      <c r="T92">
+        <v>5.478766295446169</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03343185604547688</v>
+      </c>
+      <c r="W92">
+        <v>0.2308164727763402</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2289853153799787</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2388171504577585</v>
+      </c>
+      <c r="C93">
+        <v>-3287.362511877453</v>
+      </c>
+      <c r="D93">
+        <v>488.4893272860256</v>
+      </c>
+      <c r="E93">
+        <v>1312.731136786029</v>
+      </c>
+      <c r="F93">
+        <v>3836.851839163479</v>
+      </c>
+      <c r="G93">
+        <v>61</v>
+      </c>
+      <c r="H93">
+        <v>1692.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>279.2</v>
+      </c>
+      <c r="K93">
+        <v>71.7</v>
+      </c>
+      <c r="L93">
+        <v>207.5</v>
+      </c>
+      <c r="M93">
+        <v>916.2402191922388</v>
+      </c>
+      <c r="N93">
+        <v>-708.7402191922388</v>
+      </c>
+      <c r="O93">
+        <v>-103.4760720020669</v>
+      </c>
+      <c r="P93">
+        <v>-605.2641471901719</v>
+      </c>
+      <c r="Q93">
+        <v>-533.5641471901719</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.3188258328783597</v>
+      </c>
+      <c r="T93">
+        <v>6.0875181060513</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03306447301201011</v>
+      </c>
+      <c r="W93">
+        <v>0.230904203844732</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2264689932329459</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2408171504577585</v>
+      </c>
+      <c r="C94">
+        <v>-3334.361836292045</v>
+      </c>
+      <c r="D94">
+        <v>483.6532098952086</v>
+      </c>
+      <c r="E94">
+        <v>1354.894343809804</v>
+      </c>
+      <c r="F94">
+        <v>3879.015046187254</v>
+      </c>
+      <c r="G94">
+        <v>61</v>
+      </c>
+      <c r="H94">
+        <v>1692.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>279.2</v>
+      </c>
+      <c r="K94">
+        <v>71.7</v>
+      </c>
+      <c r="L94">
+        <v>207.5</v>
+      </c>
+      <c r="M94">
+        <v>926.3087930295162</v>
+      </c>
+      <c r="N94">
+        <v>-718.8087930295162</v>
+      </c>
+      <c r="O94">
+        <v>-104.9460837823094</v>
+      </c>
+      <c r="P94">
+        <v>-613.8627092472068</v>
+      </c>
+      <c r="Q94">
+        <v>-542.1627092472067</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.3538290619881548</v>
+      </c>
+      <c r="T94">
+        <v>6.848457869307714</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03270507656622738</v>
+      </c>
+      <c r="W94">
+        <v>0.2309900277159849</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2240073737412834</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2428171504577585</v>
+      </c>
+      <c r="C95">
+        <v>-3381.266342846864</v>
+      </c>
+      <c r="D95">
+        <v>478.9119103641641</v>
+      </c>
+      <c r="E95">
+        <v>1397.057550833579</v>
+      </c>
+      <c r="F95">
+        <v>3921.178253211028</v>
+      </c>
+      <c r="G95">
+        <v>61</v>
+      </c>
+      <c r="H95">
+        <v>1692.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>279.2</v>
+      </c>
+      <c r="K95">
+        <v>71.7</v>
+      </c>
+      <c r="L95">
+        <v>207.5</v>
+      </c>
+      <c r="M95">
+        <v>936.3773668667936</v>
+      </c>
+      <c r="N95">
+        <v>-728.8773668667936</v>
+      </c>
+      <c r="O95">
+        <v>-106.4160955625519</v>
+      </c>
+      <c r="P95">
+        <v>-622.4612713042418</v>
+      </c>
+      <c r="Q95">
+        <v>-550.7612713042417</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.3988332137007484</v>
+      </c>
+      <c r="T95">
+        <v>7.826808993494531</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03235340907626794</v>
+      </c>
+      <c r="W95">
+        <v>0.2310740059125872</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2215986923032051</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2448171504577585</v>
+      </c>
+      <c r="C96">
+        <v>-3428.078792997243</v>
+      </c>
+      <c r="D96">
+        <v>474.2626672375599</v>
+      </c>
+      <c r="E96">
+        <v>1439.220757857353</v>
+      </c>
+      <c r="F96">
+        <v>3963.341460234803</v>
+      </c>
+      <c r="G96">
+        <v>61</v>
+      </c>
+      <c r="H96">
+        <v>1692.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>279.2</v>
+      </c>
+      <c r="K96">
+        <v>71.7</v>
+      </c>
+      <c r="L96">
+        <v>207.5</v>
+      </c>
+      <c r="M96">
+        <v>946.4459407040708</v>
+      </c>
+      <c r="N96">
+        <v>-738.9459407040708</v>
+      </c>
+      <c r="O96">
+        <v>-107.8861073427943</v>
+      </c>
+      <c r="P96">
+        <v>-631.0598333612766</v>
+      </c>
+      <c r="Q96">
+        <v>-559.3598333612765</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.4588387493175399</v>
+      </c>
+      <c r="T96">
+        <v>9.131277159076955</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03200922387332893</v>
+      </c>
+      <c r="W96">
+        <v>0.2311561973390491</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2192412594063625</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2468171504577585</v>
+      </c>
+      <c r="C97">
+        <v>-3474.80184199745</v>
+      </c>
+      <c r="D97">
+        <v>469.7028252611275</v>
+      </c>
+      <c r="E97">
+        <v>1481.383964881128</v>
+      </c>
+      <c r="F97">
+        <v>4005.504667258577</v>
+      </c>
+      <c r="G97">
+        <v>61</v>
+      </c>
+      <c r="H97">
+        <v>1692.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>279.2</v>
+      </c>
+      <c r="K97">
+        <v>71.7</v>
+      </c>
+      <c r="L97">
+        <v>207.5</v>
+      </c>
+      <c r="M97">
+        <v>956.5145145413483</v>
+      </c>
+      <c r="N97">
+        <v>-749.0145145413483</v>
+      </c>
+      <c r="O97">
+        <v>-109.3561191230368</v>
+      </c>
+      <c r="P97">
+        <v>-639.6583954183114</v>
+      </c>
+      <c r="Q97">
+        <v>-567.9583954183114</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.5428464991810482</v>
+      </c>
+      <c r="T97">
+        <v>10.95753259089235</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0316722846746623</v>
+      </c>
+      <c r="W97">
+        <v>0.2312366584196907</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2169334566757692</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2488171504577585</v>
+      </c>
+      <c r="C98">
+        <v>-3521.43804395747</v>
+      </c>
+      <c r="D98">
+        <v>465.229830324882</v>
+      </c>
+      <c r="E98">
+        <v>1523.547171904902</v>
+      </c>
+      <c r="F98">
+        <v>4047.667874282351</v>
+      </c>
+      <c r="G98">
+        <v>61</v>
+      </c>
+      <c r="H98">
+        <v>1692.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>279.2</v>
+      </c>
+      <c r="K98">
+        <v>71.7</v>
+      </c>
+      <c r="L98">
+        <v>207.5</v>
+      </c>
+      <c r="M98">
+        <v>966.5830883786256</v>
+      </c>
+      <c r="N98">
+        <v>-759.0830883786256</v>
+      </c>
+      <c r="O98">
+        <v>-110.8261309032793</v>
+      </c>
+      <c r="P98">
+        <v>-648.2569574753462</v>
+      </c>
+      <c r="Q98">
+        <v>-576.5569574753462</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.6688581239763087</v>
+      </c>
+      <c r="T98">
+        <v>13.69691573861541</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03134236504263457</v>
+      </c>
+      <c r="W98">
+        <v>0.2313154432278189</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.21467373316873</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2508171504577585</v>
+      </c>
+      <c r="C99">
+        <v>-3567.989856613575</v>
+      </c>
+      <c r="D99">
+        <v>460.8412246925509</v>
+      </c>
+      <c r="E99">
+        <v>1565.710378928676</v>
+      </c>
+      <c r="F99">
+        <v>4089.831081306126</v>
+      </c>
+      <c r="G99">
+        <v>61</v>
+      </c>
+      <c r="H99">
+        <v>1692.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>279.2</v>
+      </c>
+      <c r="K99">
+        <v>71.7</v>
+      </c>
+      <c r="L99">
+        <v>207.5</v>
+      </c>
+      <c r="M99">
+        <v>976.6516622159029</v>
+      </c>
+      <c r="N99">
+        <v>-769.1516622159029</v>
+      </c>
+      <c r="O99">
+        <v>-112.2961426835218</v>
+      </c>
+      <c r="P99">
+        <v>-656.8555195323811</v>
+      </c>
+      <c r="Q99">
+        <v>-585.155519532381</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>0.8788774986350785</v>
+      </c>
+      <c r="T99">
+        <v>18.26255431815388</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03101924787724659</v>
+      </c>
+      <c r="W99">
+        <v>0.2313926036069135</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2124606018989492</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2528171504577585</v>
+      </c>
+      <c r="C100">
+        <v>-3614.45964583141</v>
+      </c>
+      <c r="D100">
+        <v>456.5346424984896</v>
+      </c>
+      <c r="E100">
+        <v>1607.87358595245</v>
+      </c>
+      <c r="F100">
+        <v>4131.9942883299</v>
+      </c>
+      <c r="G100">
+        <v>61</v>
+      </c>
+      <c r="H100">
+        <v>1692.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>279.2</v>
+      </c>
+      <c r="K100">
+        <v>71.7</v>
+      </c>
+      <c r="L100">
+        <v>207.5</v>
+      </c>
+      <c r="M100">
+        <v>986.7202360531802</v>
+      </c>
+      <c r="N100">
+        <v>-779.2202360531802</v>
+      </c>
+      <c r="O100">
+        <v>-113.7661544637643</v>
+      </c>
+      <c r="P100">
+        <v>-665.4540815894159</v>
+      </c>
+      <c r="Q100">
+        <v>-593.7540815894158</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.298916247952617</v>
+      </c>
+      <c r="T100">
+        <v>27.39383147723081</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03070272493972366</v>
+      </c>
+      <c r="W100">
+        <v>0.231468189284394</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2102926365734498</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2548171504577585</v>
+      </c>
+      <c r="C101">
+        <v>-3660.849689858924</v>
+      </c>
+      <c r="D101">
+        <v>452.307805494751</v>
+      </c>
+      <c r="E101">
+        <v>1650.036792976225</v>
+      </c>
+      <c r="F101">
+        <v>4174.157495353675</v>
+      </c>
+      <c r="G101">
+        <v>61</v>
+      </c>
+      <c r="H101">
+        <v>1692.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>279.2</v>
+      </c>
+      <c r="K101">
+        <v>71.7</v>
+      </c>
+      <c r="L101">
+        <v>207.5</v>
+      </c>
+      <c r="M101">
+        <v>996.7888098904575</v>
+      </c>
+      <c r="N101">
+        <v>-789.2888098904575</v>
+      </c>
+      <c r="O101">
+        <v>-115.2361662440068</v>
+      </c>
+      <c r="P101">
+        <v>-674.0526436464507</v>
+      </c>
+      <c r="Q101">
+        <v>-602.3526436464507</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>2.559032495905235</v>
+      </c>
+      <c r="T101">
+        <v>54.78766295446164</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03039259640497898</v>
+      </c>
+      <c r="W101">
+        <v>0.231542247978491</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2081684685272533</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
